--- a/Comentários.xlsx
+++ b/Comentários.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iterpar-my.sharepoint.com/personal/emilly_viana_iter_com_br/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="337" documentId="8_{403DAE47-8640-46F3-9B3C-EED202671176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{218CA88B-45B3-40D5-9984-47756CE7CB43}"/>
+  <xr:revisionPtr revIDLastSave="338" documentId="8_{403DAE47-8640-46F3-9B3C-EED202671176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EE6E156-3DB2-4C3B-95E6-713D217F6C89}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{35DF3EEB-C7CA-4F2F-980A-D89CB0EF8D20}"/>
   </bookViews>
@@ -2049,8 +2049,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
+  <numFmts count="1">
     <numFmt numFmtId="165" formatCode="mm/yyyy"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
@@ -2100,7 +2099,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2112,9 +2111,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2132,34 +2128,7 @@
   </cellStyles>
   <dxfs count="20">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="165" formatCode="mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2195,6 +2164,34 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2213,35 +2210,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{18856368-ED83-4C24-81B2-5E9BC9A92189}" name="Tabela2" displayName="Tabela2" ref="A1:H125" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{18856368-ED83-4C24-81B2-5E9BC9A92189}" name="Tabela2" displayName="Tabela2" ref="A1:H125" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A1:H125" xr:uid="{18856368-ED83-4C24-81B2-5E9BC9A92189}"/>
   <tableColumns count="8">
-    <tableColumn id="8" xr3:uid="{A262542A-8935-42A6-8200-27E78003948D}" name="Fonte" dataDxfId="0"/>
-    <tableColumn id="1" xr3:uid="{C44C9CDE-4F93-4B57-88FA-B5F379ED3637}" name="Data de publicação" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{B6AAEB8D-FC7B-4CB8-AAB0-8B2A961BB4A6}" name="Data de visitação" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{753E2221-D3DF-4906-BCF8-BF9B055849C8}" name="Comentário" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{21EBB58E-1B0E-4D25-84B2-A36564A2A6C6}" name="Pontuação" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{6D352639-39AD-45EA-AE78-EAF33B5CC611}" name="Companhia" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{7422250C-9A9E-4CD8-AF2C-8352F10B7C22}" name="Origem" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{B3427257-C97F-4470-9E10-FD2D90DE77F3}" name="Tipo" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{A262542A-8935-42A6-8200-27E78003948D}" name="Fonte" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{C44C9CDE-4F93-4B57-88FA-B5F379ED3637}" name="Data de publicação" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{B6AAEB8D-FC7B-4CB8-AAB0-8B2A961BB4A6}" name="Data de visitação" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{753E2221-D3DF-4906-BCF8-BF9B055849C8}" name="Comentário" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{21EBB58E-1B0E-4D25-84B2-A36564A2A6C6}" name="Pontuação" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{6D352639-39AD-45EA-AE78-EAF33B5CC611}" name="Companhia" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{7422250C-9A9E-4CD8-AF2C-8352F10B7C22}" name="Origem" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{B3427257-C97F-4470-9E10-FD2D90DE77F3}" name="Tipo" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7EB8E621-8EAE-450C-A334-9A2E4CC8A358}" name="Tabela1" displayName="Tabela1" ref="A1:F353" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7EB8E621-8EAE-450C-A334-9A2E4CC8A358}" name="Tabela1" displayName="Tabela1" ref="A1:F353" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A1:F353" xr:uid="{7EB8E621-8EAE-450C-A334-9A2E4CC8A358}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F246">
     <sortCondition ref="C1:C246"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="6" xr3:uid="{ABBA6451-C423-46F6-B566-E237B2E52E6D}" name="Fonte" dataDxfId="17"/>
-    <tableColumn id="1" xr3:uid="{BF661C3B-1DFD-40DC-B369-A40C5952DCCF}" name="Data de publicação" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{59453DB2-9038-4720-ABE9-C50568ED337F}" name="Data de visitação" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{1161D8C4-4F9B-4D9D-8C23-8FCA093DCCB1}" name="Comentário" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{A83E9465-2EB5-44D3-AA56-00B6CFDC9AF5}" name="Pontuação" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{2AE2C9E4-2F91-4805-A0EF-77102FC0EBA9}" name="Companhia" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{ABBA6451-C423-46F6-B566-E237B2E52E6D}" name="Fonte" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{BF661C3B-1DFD-40DC-B369-A40C5952DCCF}" name="Data de publicação" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{59453DB2-9038-4720-ABE9-C50568ED337F}" name="Data de visitação" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{1161D8C4-4F9B-4D9D-8C23-8FCA093DCCB1}" name="Comentário" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{A83E9465-2EB5-44D3-AA56-00B6CFDC9AF5}" name="Pontuação" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{2AE2C9E4-2F91-4805-A0EF-77102FC0EBA9}" name="Companhia" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2583,7 +2580,7 @@
   <cols>
     <col min="1" max="1" width="20.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="21" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="43.7109375" style="5" customWidth="1"/>
     <col min="4" max="4" width="27.5703125" style="2" customWidth="1"/>
     <col min="5" max="5" width="13.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -2624,7 +2621,7 @@
       <c r="B2" s="4">
         <v>46214</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>46204</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -2650,7 +2647,7 @@
       <c r="B3" s="4">
         <v>46218</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>46205</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -2676,7 +2673,7 @@
       <c r="B4" s="4">
         <v>46219</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>46206</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -2702,7 +2699,7 @@
       <c r="B5" s="4">
         <v>46222</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>46207</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -2721,14 +2718,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="240" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="225" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B6" s="4">
         <v>46224</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>46208</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -2754,7 +2751,7 @@
       <c r="B7" s="4">
         <v>46224</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>46209</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2777,10 +2774,10 @@
       <c r="A8" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>46023</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>46023</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -2797,10 +2794,10 @@
       <c r="A9" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>46024</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>46023</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -2820,7 +2817,7 @@
       <c r="B10" s="4">
         <v>46025</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>46023</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -2833,14 +2830,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B11" s="4">
         <v>46028</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>46023</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -2857,7 +2854,7 @@
       <c r="B12" s="4">
         <v>46032</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>46023</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -2877,7 +2874,7 @@
       <c r="B13" s="4">
         <v>46035</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>46023</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -2897,7 +2894,7 @@
       <c r="B14" s="4">
         <v>46036</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>46023</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -2907,14 +2904,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="225" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B15" s="4">
         <v>46037</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>46023</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -2931,7 +2928,7 @@
       <c r="B16" s="4">
         <v>46040</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>46023</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -2951,7 +2948,7 @@
       <c r="B17" s="4">
         <v>46050</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>46023</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -2968,7 +2965,7 @@
       <c r="B18" s="4">
         <v>46058</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>46054</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -2988,7 +2985,7 @@
       <c r="B19" s="4">
         <v>46065</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>46054</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -3001,14 +2998,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="195" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="180" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B20" s="4">
         <v>46065</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>46054</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -3021,14 +3018,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="285" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="270" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B21" s="4">
         <v>46074</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>46054</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -3045,7 +3042,7 @@
       <c r="B22" s="4">
         <v>46086</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>46082</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -3065,7 +3062,7 @@
       <c r="B23" s="4">
         <v>46089</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>46023</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -3085,7 +3082,7 @@
       <c r="B24" s="4">
         <v>46093</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <v>46082</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -3105,7 +3102,7 @@
       <c r="B25" s="4">
         <v>46094</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <v>46082</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -3125,7 +3122,7 @@
       <c r="B26" s="4">
         <v>46098</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <v>46082</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -3145,7 +3142,7 @@
       <c r="B27" s="4">
         <v>46102</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>46054</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -3165,7 +3162,7 @@
       <c r="B28" s="4">
         <v>46103</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="5">
         <v>46023</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -3182,7 +3179,7 @@
       <c r="B29" s="4">
         <v>46114</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <v>46113</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -3202,7 +3199,7 @@
       <c r="B30" s="4">
         <v>46115</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="5">
         <v>46082</v>
       </c>
       <c r="D30" s="3" t="s">
@@ -3222,7 +3219,7 @@
       <c r="B31" s="4">
         <v>46115</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>46113</v>
       </c>
       <c r="D31" s="3" t="s">
@@ -3232,14 +3229,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="390" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="375" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B32" s="4">
         <v>46116</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="5">
         <v>46113</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -3249,14 +3246,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="330" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="315" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B33" s="4">
         <v>46117</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>46113</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -3273,7 +3270,7 @@
       <c r="B34" s="4">
         <v>46123</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="5">
         <v>46082</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -3293,7 +3290,7 @@
       <c r="B35" s="4">
         <v>46129</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="5">
         <v>46082</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -3313,7 +3310,7 @@
       <c r="B36" s="4">
         <v>46129</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="5">
         <v>46113</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -3333,7 +3330,7 @@
       <c r="B37" s="4">
         <v>46133</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="5">
         <v>46113</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -3350,7 +3347,7 @@
       <c r="B38" s="4">
         <v>46135</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="5">
         <v>46113</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -3370,7 +3367,7 @@
       <c r="B39" s="4">
         <v>46135</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="5">
         <v>46113</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -3387,7 +3384,7 @@
       <c r="B40" s="4">
         <v>46138</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="5">
         <v>46113</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -3404,7 +3401,7 @@
       <c r="B41" s="4">
         <v>46140</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="5">
         <v>46113</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -3421,7 +3418,7 @@
       <c r="B42" s="4">
         <v>46141</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="5">
         <v>45809</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -3438,7 +3435,7 @@
       <c r="B43" s="4">
         <v>46150</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="5">
         <v>46143</v>
       </c>
       <c r="D43" s="3" t="s">
@@ -3458,7 +3455,7 @@
       <c r="B44" s="4">
         <v>46154</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="5">
         <v>46143</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -3478,7 +3475,7 @@
       <c r="B45" s="4">
         <v>46159</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="5">
         <v>46143</v>
       </c>
       <c r="D45" s="3" t="s">
@@ -3498,7 +3495,7 @@
       <c r="B46" s="4">
         <v>46166</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="5">
         <v>46143</v>
       </c>
       <c r="D46" s="3" t="s">
@@ -3515,7 +3512,7 @@
       <c r="B47" s="4">
         <v>46179</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="5">
         <v>46174</v>
       </c>
       <c r="D47" s="3" t="s">
@@ -3532,7 +3529,7 @@
       <c r="B48" s="4">
         <v>46188</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="5">
         <v>46174</v>
       </c>
       <c r="D48" s="3" t="s">
@@ -3552,7 +3549,7 @@
       <c r="B49" s="4">
         <v>46192</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="5">
         <v>46174</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -3572,7 +3569,7 @@
       <c r="B50" s="4">
         <v>46201</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="5">
         <v>46174</v>
       </c>
       <c r="D50" s="3" t="s">
@@ -3592,7 +3589,7 @@
       <c r="B51" s="4">
         <v>46223</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="5">
         <v>46113</v>
       </c>
       <c r="D51" s="3" t="s">
@@ -3612,7 +3609,7 @@
       <c r="B52" s="4">
         <v>45658</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="5">
         <v>45658</v>
       </c>
       <c r="D52" s="3" t="s">
@@ -3629,7 +3626,7 @@
       <c r="B53" s="4">
         <v>45658</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="5">
         <v>45658</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -3646,7 +3643,7 @@
       <c r="B54" s="4">
         <v>45658</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="5">
         <v>45658</v>
       </c>
       <c r="D54" s="3" t="s">
@@ -3663,7 +3660,7 @@
       <c r="B55" s="4">
         <v>45658</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="5">
         <v>45658</v>
       </c>
       <c r="D55" s="3" t="s">
@@ -3680,7 +3677,7 @@
       <c r="B56" s="4">
         <v>45658</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="5">
         <v>45658</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -3697,7 +3694,7 @@
       <c r="B57" s="4">
         <v>45658</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="5">
         <v>45658</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -3714,7 +3711,7 @@
       <c r="B58" s="4">
         <v>45658</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="5">
         <v>45658</v>
       </c>
       <c r="D58" s="3" t="s">
@@ -3731,7 +3728,7 @@
       <c r="B59" s="4">
         <v>45658</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="5">
         <v>45658</v>
       </c>
       <c r="D59" s="3" t="s">
@@ -3748,7 +3745,7 @@
       <c r="B60" s="4">
         <v>45658</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="5">
         <v>45658</v>
       </c>
       <c r="D60" s="3" t="s">
@@ -3765,7 +3762,7 @@
       <c r="B61" s="4">
         <v>45658</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="5">
         <v>45658</v>
       </c>
       <c r="D61" s="3" t="s">
@@ -3782,7 +3779,7 @@
       <c r="B62" s="4">
         <v>45689</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="5">
         <v>45689</v>
       </c>
       <c r="D62" s="3" t="s">
@@ -3799,7 +3796,7 @@
       <c r="B63" s="4">
         <v>45689</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="5">
         <v>45689</v>
       </c>
       <c r="D63" s="3" t="s">
@@ -3816,7 +3813,7 @@
       <c r="B64" s="4">
         <v>45689</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="5">
         <v>45689</v>
       </c>
       <c r="D64" s="3" t="s">
@@ -3833,7 +3830,7 @@
       <c r="B65" s="4">
         <v>45689</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="5">
         <v>45689</v>
       </c>
       <c r="D65" s="3" t="s">
@@ -3850,7 +3847,7 @@
       <c r="B66" s="4">
         <v>45689</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="5">
         <v>45689</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -3867,7 +3864,7 @@
       <c r="B67" s="4">
         <v>45689</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67" s="5">
         <v>45689</v>
       </c>
       <c r="D67" s="3" t="s">
@@ -3884,7 +3881,7 @@
       <c r="B68" s="4">
         <v>45689</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68" s="5">
         <v>45689</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -3901,7 +3898,7 @@
       <c r="B69" s="4">
         <v>45689</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="5">
         <v>45689</v>
       </c>
       <c r="D69" s="3" t="s">
@@ -3918,7 +3915,7 @@
       <c r="B70" s="4">
         <v>45689</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="5">
         <v>45689</v>
       </c>
       <c r="D70" s="3" t="s">
@@ -3935,7 +3932,7 @@
       <c r="B71" s="4">
         <v>45717</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="5">
         <v>45717</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -3952,7 +3949,7 @@
       <c r="B72" s="4">
         <v>45717</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="5">
         <v>45717</v>
       </c>
       <c r="D72" s="3" t="s">
@@ -3969,7 +3966,7 @@
       <c r="B73" s="4">
         <v>45717</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73" s="5">
         <v>45717</v>
       </c>
       <c r="D73" s="3" t="s">
@@ -3986,7 +3983,7 @@
       <c r="B74" s="4">
         <v>45717</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74" s="5">
         <v>45717</v>
       </c>
       <c r="D74" s="3" t="s">
@@ -4003,7 +4000,7 @@
       <c r="B75" s="4">
         <v>45717</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75" s="5">
         <v>45717</v>
       </c>
       <c r="D75" s="3" t="s">
@@ -4020,7 +4017,7 @@
       <c r="B76" s="4">
         <v>45717</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76" s="5">
         <v>45717</v>
       </c>
       <c r="D76" s="3" t="s">
@@ -4037,7 +4034,7 @@
       <c r="B77" s="4">
         <v>45717</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77" s="5">
         <v>45717</v>
       </c>
       <c r="D77" s="3" t="s">
@@ -4054,7 +4051,7 @@
       <c r="B78" s="4">
         <v>45748</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78" s="5">
         <v>45748</v>
       </c>
       <c r="D78" s="3" t="s">
@@ -4071,7 +4068,7 @@
       <c r="B79" s="4">
         <v>45748</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79" s="5">
         <v>45748</v>
       </c>
       <c r="D79" s="3" t="s">
@@ -4088,7 +4085,7 @@
       <c r="B80" s="4">
         <v>45931</v>
       </c>
-      <c r="C80" s="4">
+      <c r="C80" s="5">
         <v>45931</v>
       </c>
       <c r="D80" s="3" t="s">
@@ -4105,7 +4102,7 @@
       <c r="B81" s="4">
         <v>45931</v>
       </c>
-      <c r="C81" s="4">
+      <c r="C81" s="5">
         <v>45931</v>
       </c>
       <c r="D81" s="3" t="s">
@@ -4122,7 +4119,7 @@
       <c r="B82" s="4">
         <v>45931</v>
       </c>
-      <c r="C82" s="4">
+      <c r="C82" s="5">
         <v>45931</v>
       </c>
       <c r="D82" s="3" t="s">
@@ -4139,7 +4136,7 @@
       <c r="B83" s="4">
         <v>45931</v>
       </c>
-      <c r="C83" s="4">
+      <c r="C83" s="5">
         <v>45931</v>
       </c>
       <c r="D83" s="3" t="s">
@@ -4156,7 +4153,7 @@
       <c r="B84" s="4">
         <v>45992</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84" s="5">
         <v>45992</v>
       </c>
       <c r="D84" s="3" t="s">
@@ -4173,7 +4170,7 @@
       <c r="B85" s="4">
         <v>45992</v>
       </c>
-      <c r="C85" s="4">
+      <c r="C85" s="5">
         <v>45992</v>
       </c>
       <c r="D85" s="3" t="s">
@@ -4190,7 +4187,7 @@
       <c r="B86" s="4">
         <v>45992</v>
       </c>
-      <c r="C86" s="4">
+      <c r="C86" s="5">
         <v>45992</v>
       </c>
       <c r="D86" s="3" t="s">
@@ -4207,7 +4204,7 @@
       <c r="B87" s="4">
         <v>45992</v>
       </c>
-      <c r="C87" s="4">
+      <c r="C87" s="5">
         <v>45992</v>
       </c>
       <c r="D87" s="3" t="s">
@@ -4224,7 +4221,7 @@
       <c r="B88" s="4">
         <v>45992</v>
       </c>
-      <c r="C88" s="4">
+      <c r="C88" s="5">
         <v>45992</v>
       </c>
       <c r="D88" s="3" t="s">
@@ -4241,7 +4238,7 @@
       <c r="B89" s="4">
         <v>46023</v>
       </c>
-      <c r="C89" s="4">
+      <c r="C89" s="5">
         <v>46023</v>
       </c>
       <c r="D89" s="3" t="s">
@@ -4258,7 +4255,7 @@
       <c r="B90" s="4">
         <v>46023</v>
       </c>
-      <c r="C90" s="4">
+      <c r="C90" s="5">
         <v>46023</v>
       </c>
       <c r="D90" s="3" t="s">
@@ -4275,7 +4272,7 @@
       <c r="B91" s="4">
         <v>46023</v>
       </c>
-      <c r="C91" s="4">
+      <c r="C91" s="5">
         <v>46023</v>
       </c>
       <c r="D91" s="3" t="s">
@@ -4292,7 +4289,7 @@
       <c r="B92" s="4">
         <v>46023</v>
       </c>
-      <c r="C92" s="4">
+      <c r="C92" s="5">
         <v>46023</v>
       </c>
       <c r="D92" s="3" t="s">
@@ -4309,7 +4306,7 @@
       <c r="B93" s="4">
         <v>46023</v>
       </c>
-      <c r="C93" s="4">
+      <c r="C93" s="5">
         <v>46023</v>
       </c>
       <c r="D93" s="3" t="s">
@@ -4326,7 +4323,7 @@
       <c r="B94" s="4">
         <v>46023</v>
       </c>
-      <c r="C94" s="4">
+      <c r="C94" s="5">
         <v>46023</v>
       </c>
       <c r="D94" s="3" t="s">
@@ -4343,7 +4340,7 @@
       <c r="B95" s="4">
         <v>46054</v>
       </c>
-      <c r="C95" s="4">
+      <c r="C95" s="5">
         <v>46054</v>
       </c>
       <c r="D95" s="3" t="s">
@@ -4360,7 +4357,7 @@
       <c r="B96" s="4">
         <v>46054</v>
       </c>
-      <c r="C96" s="4">
+      <c r="C96" s="5">
         <v>46054</v>
       </c>
       <c r="D96" s="3" t="s">
@@ -4377,7 +4374,7 @@
       <c r="B97" s="4">
         <v>46054</v>
       </c>
-      <c r="C97" s="4">
+      <c r="C97" s="5">
         <v>46054</v>
       </c>
       <c r="D97" s="3" t="s">
@@ -4394,7 +4391,7 @@
       <c r="B98" s="4">
         <v>46054</v>
       </c>
-      <c r="C98" s="4">
+      <c r="C98" s="5">
         <v>46054</v>
       </c>
       <c r="D98" s="3" t="s">
@@ -4411,7 +4408,7 @@
       <c r="B99" s="4">
         <v>46054</v>
       </c>
-      <c r="C99" s="4">
+      <c r="C99" s="5">
         <v>46054</v>
       </c>
       <c r="D99" s="3" t="s">
@@ -4428,7 +4425,7 @@
       <c r="B100" s="4">
         <v>46054</v>
       </c>
-      <c r="C100" s="4">
+      <c r="C100" s="5">
         <v>46054</v>
       </c>
       <c r="D100" s="3" t="s">
@@ -4445,7 +4442,7 @@
       <c r="B101" s="4">
         <v>46054</v>
       </c>
-      <c r="C101" s="4">
+      <c r="C101" s="5">
         <v>46054</v>
       </c>
       <c r="D101" s="3" t="s">
@@ -4462,7 +4459,7 @@
       <c r="B102" s="4">
         <v>46054</v>
       </c>
-      <c r="C102" s="4">
+      <c r="C102" s="5">
         <v>46054</v>
       </c>
       <c r="D102" s="3" t="s">
@@ -4479,7 +4476,7 @@
       <c r="B103" s="4">
         <v>46054</v>
       </c>
-      <c r="C103" s="4">
+      <c r="C103" s="5">
         <v>46054</v>
       </c>
       <c r="D103" s="3" t="s">
@@ -4496,7 +4493,7 @@
       <c r="B104" s="4">
         <v>46054</v>
       </c>
-      <c r="C104" s="4">
+      <c r="C104" s="5">
         <v>46054</v>
       </c>
       <c r="D104" s="3" t="s">
@@ -4513,7 +4510,7 @@
       <c r="B105" s="4">
         <v>46082</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105" s="5">
         <v>46082</v>
       </c>
       <c r="D105" s="3" t="s">
@@ -4530,7 +4527,7 @@
       <c r="B106" s="4">
         <v>46082</v>
       </c>
-      <c r="C106" s="4">
+      <c r="C106" s="5">
         <v>46082</v>
       </c>
       <c r="D106" s="3" t="s">
@@ -4547,7 +4544,7 @@
       <c r="B107" s="4">
         <v>46082</v>
       </c>
-      <c r="C107" s="4">
+      <c r="C107" s="5">
         <v>46082</v>
       </c>
       <c r="D107" s="3" t="s">
@@ -4564,7 +4561,7 @@
       <c r="B108" s="4">
         <v>46082</v>
       </c>
-      <c r="C108" s="4">
+      <c r="C108" s="5">
         <v>46082</v>
       </c>
       <c r="D108" s="3" t="s">
@@ -4581,7 +4578,7 @@
       <c r="B109" s="4">
         <v>46082</v>
       </c>
-      <c r="C109" s="4">
+      <c r="C109" s="5">
         <v>46082</v>
       </c>
       <c r="D109" s="3" t="s">
@@ -4598,7 +4595,7 @@
       <c r="B110" s="4">
         <v>46082</v>
       </c>
-      <c r="C110" s="4">
+      <c r="C110" s="5">
         <v>46082</v>
       </c>
       <c r="D110" s="3" t="s">
@@ -4615,7 +4612,7 @@
       <c r="B111" s="4">
         <v>46082</v>
       </c>
-      <c r="C111" s="4">
+      <c r="C111" s="5">
         <v>46082</v>
       </c>
       <c r="D111" s="3" t="s">
@@ -4632,7 +4629,7 @@
       <c r="B112" s="4">
         <v>46082</v>
       </c>
-      <c r="C112" s="4">
+      <c r="C112" s="5">
         <v>46082</v>
       </c>
       <c r="D112" s="3" t="s">
@@ -4649,7 +4646,7 @@
       <c r="B113" s="4">
         <v>46082</v>
       </c>
-      <c r="C113" s="4">
+      <c r="C113" s="5">
         <v>46082</v>
       </c>
       <c r="D113" s="3" t="s">
@@ -4666,7 +4663,7 @@
       <c r="B114" s="4">
         <v>46082</v>
       </c>
-      <c r="C114" s="4">
+      <c r="C114" s="5">
         <v>46082</v>
       </c>
       <c r="D114" s="3" t="s">
@@ -4683,7 +4680,7 @@
       <c r="B115" s="4">
         <v>46113</v>
       </c>
-      <c r="C115" s="4">
+      <c r="C115" s="5">
         <v>46113</v>
       </c>
       <c r="D115" s="3" t="s">
@@ -4700,7 +4697,7 @@
       <c r="B116" s="4">
         <v>46113</v>
       </c>
-      <c r="C116" s="4">
+      <c r="C116" s="5">
         <v>46113</v>
       </c>
       <c r="D116" s="3" t="s">
@@ -4717,7 +4714,7 @@
       <c r="B117" s="4">
         <v>46113</v>
       </c>
-      <c r="C117" s="4">
+      <c r="C117" s="5">
         <v>46113</v>
       </c>
       <c r="D117" s="3" t="s">
@@ -4734,7 +4731,7 @@
       <c r="B118" s="4">
         <v>46113</v>
       </c>
-      <c r="C118" s="4">
+      <c r="C118" s="5">
         <v>46113</v>
       </c>
       <c r="D118" s="3" t="s">
@@ -4751,7 +4748,7 @@
       <c r="B119" s="4">
         <v>46113</v>
       </c>
-      <c r="C119" s="4">
+      <c r="C119" s="5">
         <v>46113</v>
       </c>
       <c r="D119" s="3" t="s">
@@ -4768,7 +4765,7 @@
       <c r="B120" s="4">
         <v>46113</v>
       </c>
-      <c r="C120" s="4">
+      <c r="C120" s="5">
         <v>46113</v>
       </c>
       <c r="D120" s="3" t="s">
@@ -4785,7 +4782,7 @@
       <c r="B121" s="4">
         <v>46143</v>
       </c>
-      <c r="C121" s="4">
+      <c r="C121" s="5">
         <v>46143</v>
       </c>
       <c r="D121" s="3" t="s">
@@ -4802,7 +4799,7 @@
       <c r="B122" s="4">
         <v>46143</v>
       </c>
-      <c r="C122" s="4">
+      <c r="C122" s="5">
         <v>46143</v>
       </c>
       <c r="D122" s="3" t="s">
@@ -4819,7 +4816,7 @@
       <c r="B123" s="4">
         <v>46143</v>
       </c>
-      <c r="C123" s="4">
+      <c r="C123" s="5">
         <v>46143</v>
       </c>
       <c r="D123" s="3" t="s">
@@ -4836,7 +4833,7 @@
       <c r="B124" s="4">
         <v>46143</v>
       </c>
-      <c r="C124" s="4">
+      <c r="C124" s="5">
         <v>46143</v>
       </c>
       <c r="D124" s="3" t="s">
@@ -4853,7 +4850,7 @@
       <c r="B125" s="4">
         <v>46143</v>
       </c>
-      <c r="C125" s="4">
+      <c r="C125" s="5">
         <v>46143</v>
       </c>
       <c r="D125" s="3" t="s">
@@ -4878,7 +4875,7 @@
   <cols>
     <col min="1" max="1" width="36.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="21" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.85546875" style="3"/>
     <col min="5" max="5" width="21.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="21" style="2" customWidth="1"/>
@@ -4892,7 +4889,7 @@
       <c r="B1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -4912,7 +4909,7 @@
       <c r="B2" s="4">
         <v>46021</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>45658</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -4932,7 +4929,7 @@
       <c r="B3" s="4">
         <v>45920</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>45658</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -4952,7 +4949,7 @@
       <c r="B4" s="4">
         <v>45891</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>45658</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -4972,7 +4969,7 @@
       <c r="B5" s="4">
         <v>45783</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>45658</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -4992,7 +4989,7 @@
       <c r="B6" s="4">
         <v>45733</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>45658</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -5012,7 +5009,7 @@
       <c r="B7" s="4">
         <v>45721</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>45658</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -5032,7 +5029,7 @@
       <c r="B8" s="4">
         <v>45701</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>45658</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -5045,14 +5042,14 @@
         <v>268</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="375" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="345" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B9" s="4">
         <v>45701</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>45658</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -5072,7 +5069,7 @@
       <c r="B10" s="4">
         <v>45696</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>45658</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -5092,7 +5089,7 @@
       <c r="B11" s="4">
         <v>45691</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>45658</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -5112,7 +5109,7 @@
       <c r="B12" s="4">
         <v>45688</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>45658</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -5132,7 +5129,7 @@
       <c r="B13" s="4">
         <v>45684</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>45658</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -5152,7 +5149,7 @@
       <c r="B14" s="4">
         <v>45684</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>45658</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -5172,7 +5169,7 @@
       <c r="B15" s="4">
         <v>45683</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>45658</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -5192,7 +5189,7 @@
       <c r="B16" s="4">
         <v>45683</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>45658</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -5212,7 +5209,7 @@
       <c r="B17" s="4">
         <v>45683</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>45658</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -5232,7 +5229,7 @@
       <c r="B18" s="4">
         <v>45683</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>45658</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -5252,7 +5249,7 @@
       <c r="B19" s="4">
         <v>45683</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>45658</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -5272,7 +5269,7 @@
       <c r="B20" s="4">
         <v>45683</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>45658</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -5292,7 +5289,7 @@
       <c r="B21" s="4">
         <v>45682</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>45658</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -5312,7 +5309,7 @@
       <c r="B22" s="4">
         <v>45680</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>45658</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -5332,7 +5329,7 @@
       <c r="B23" s="4">
         <v>45678</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>45658</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -5345,14 +5342,14 @@
         <v>268</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="300" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="285" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B24" s="4">
         <v>45678</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <v>45658</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -5372,7 +5369,7 @@
       <c r="B25" s="4">
         <v>45673</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <v>45658</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -5392,7 +5389,7 @@
       <c r="B26" s="4">
         <v>45672</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <v>45658</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -5412,7 +5409,7 @@
       <c r="B27" s="4">
         <v>45667</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>45658</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -5432,7 +5429,7 @@
       <c r="B28" s="4">
         <v>45667</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="5">
         <v>45658</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -5452,7 +5449,7 @@
       <c r="B29" s="4">
         <v>45663</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <v>45658</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -5472,7 +5469,7 @@
       <c r="B30" s="4">
         <v>45661</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="5">
         <v>45658</v>
       </c>
       <c r="D30" s="3" t="s">
@@ -5492,7 +5489,7 @@
       <c r="B31" s="4">
         <v>45660</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>45658</v>
       </c>
       <c r="D31" s="3" t="s">
@@ -5512,7 +5509,7 @@
       <c r="B32" s="4">
         <v>45659</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="5">
         <v>45658</v>
       </c>
       <c r="D32" s="3" t="s">
@@ -5532,7 +5529,7 @@
       <c r="B33" s="4">
         <v>46023</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>45689</v>
       </c>
       <c r="D33" s="3" t="s">
@@ -5552,7 +5549,7 @@
       <c r="B34" s="4">
         <v>45806</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="5">
         <v>45689</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -5572,7 +5569,7 @@
       <c r="B35" s="4">
         <v>45729</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="5">
         <v>45689</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -5592,7 +5589,7 @@
       <c r="B36" s="4">
         <v>45729</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="5">
         <v>45689</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -5612,7 +5609,7 @@
       <c r="B37" s="4">
         <v>45728</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="5">
         <v>45689</v>
       </c>
       <c r="D37" s="3" t="s">
@@ -5632,7 +5629,7 @@
       <c r="B38" s="4">
         <v>45726</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="5">
         <v>45689</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -5652,7 +5649,7 @@
       <c r="B39" s="4">
         <v>45721</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="5">
         <v>45689</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -5672,7 +5669,7 @@
       <c r="B40" s="4">
         <v>45713</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="5">
         <v>45689</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -5692,7 +5689,7 @@
       <c r="B41" s="4">
         <v>45708</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="5">
         <v>45689</v>
       </c>
       <c r="D41" s="3" t="s">
@@ -5712,7 +5709,7 @@
       <c r="B42" s="4">
         <v>45707</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="5">
         <v>45689</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -5732,7 +5729,7 @@
       <c r="B43" s="4">
         <v>45706</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="5">
         <v>45689</v>
       </c>
       <c r="D43" s="3" t="s">
@@ -5752,7 +5749,7 @@
       <c r="B44" s="4">
         <v>45705</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="5">
         <v>45689</v>
       </c>
       <c r="D44" s="3" t="s">
@@ -5772,7 +5769,7 @@
       <c r="B45" s="4">
         <v>45703</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="5">
         <v>45689</v>
       </c>
       <c r="D45" s="3" t="s">
@@ -5792,7 +5789,7 @@
       <c r="B46" s="4">
         <v>45702</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="5">
         <v>45689</v>
       </c>
       <c r="D46" s="3" t="s">
@@ -5812,7 +5809,7 @@
       <c r="B47" s="4">
         <v>45698</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="5">
         <v>45689</v>
       </c>
       <c r="D47" s="3" t="s">
@@ -5832,7 +5829,7 @@
       <c r="B48" s="4">
         <v>45698</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="5">
         <v>45689</v>
       </c>
       <c r="D48" s="3" t="s">
@@ -5852,7 +5849,7 @@
       <c r="B49" s="4">
         <v>45696</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="5">
         <v>45689</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -5872,7 +5869,7 @@
       <c r="B50" s="4">
         <v>46073</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="5">
         <v>45717</v>
       </c>
       <c r="D50" s="3" t="s">
@@ -5892,7 +5889,7 @@
       <c r="B51" s="4">
         <v>45913</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="5">
         <v>45717</v>
       </c>
       <c r="D51" s="3" t="s">
@@ -5912,7 +5909,7 @@
       <c r="B52" s="4">
         <v>45815</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="5">
         <v>45717</v>
       </c>
       <c r="D52" s="3" t="s">
@@ -5932,7 +5929,7 @@
       <c r="B53" s="4">
         <v>45755</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53" s="5">
         <v>45717</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -5952,7 +5949,7 @@
       <c r="B54" s="4">
         <v>45750</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="5">
         <v>45717</v>
       </c>
       <c r="D54" s="3" t="s">
@@ -5972,7 +5969,7 @@
       <c r="B55" s="4">
         <v>45744</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="5">
         <v>45717</v>
       </c>
       <c r="D55" s="3" t="s">
@@ -5992,7 +5989,7 @@
       <c r="B56" s="4">
         <v>45740</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="5">
         <v>45717</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -6005,14 +6002,14 @@
         <v>268</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="315" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="300" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B57" s="4">
         <v>45739</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="5">
         <v>45717</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -6032,7 +6029,7 @@
       <c r="B58" s="4">
         <v>45737</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="5">
         <v>45717</v>
       </c>
       <c r="D58" s="3" t="s">
@@ -6052,7 +6049,7 @@
       <c r="B59" s="4">
         <v>45734</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="5">
         <v>45717</v>
       </c>
       <c r="D59" s="3" t="s">
@@ -6072,7 +6069,7 @@
       <c r="B60" s="4">
         <v>45732</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="5">
         <v>45717</v>
       </c>
       <c r="D60" s="3" t="s">
@@ -6092,7 +6089,7 @@
       <c r="B61" s="4">
         <v>45729</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="5">
         <v>45717</v>
       </c>
       <c r="D61" s="3" t="s">
@@ -6112,7 +6109,7 @@
       <c r="B62" s="4">
         <v>45726</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="5">
         <v>45717</v>
       </c>
       <c r="D62" s="3" t="s">
@@ -6132,7 +6129,7 @@
       <c r="B63" s="4">
         <v>45725</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63" s="5">
         <v>45717</v>
       </c>
       <c r="D63" s="3" t="s">
@@ -6152,7 +6149,7 @@
       <c r="B64" s="4">
         <v>45724</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C64" s="5">
         <v>45717</v>
       </c>
       <c r="D64" s="3" t="s">
@@ -6172,7 +6169,7 @@
       <c r="B65" s="4">
         <v>45721</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65" s="5">
         <v>45717</v>
       </c>
       <c r="D65" s="3" t="s">
@@ -6192,7 +6189,7 @@
       <c r="B66" s="4">
         <v>46090</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C66" s="5">
         <v>45748</v>
       </c>
       <c r="D66" s="3" t="s">
@@ -6212,7 +6209,7 @@
       <c r="B67" s="4">
         <v>45788</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C67" s="5">
         <v>45748</v>
       </c>
       <c r="D67" s="3" t="s">
@@ -6232,7 +6229,7 @@
       <c r="B68" s="4">
         <v>45781</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="5">
         <v>45748</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -6252,7 +6249,7 @@
       <c r="B69" s="4">
         <v>45775</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C69" s="5">
         <v>45748</v>
       </c>
       <c r="D69" s="3" t="s">
@@ -6272,7 +6269,7 @@
       <c r="B70" s="4">
         <v>45774</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70" s="5">
         <v>45748</v>
       </c>
       <c r="D70" s="3" t="s">
@@ -6292,7 +6289,7 @@
       <c r="B71" s="4">
         <v>45771</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71" s="5">
         <v>45748</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -6312,7 +6309,7 @@
       <c r="B72" s="4">
         <v>45771</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72" s="5">
         <v>45748</v>
       </c>
       <c r="D72" s="3" t="s">
@@ -6332,7 +6329,7 @@
       <c r="B73" s="4">
         <v>45769</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C73" s="5">
         <v>45748</v>
       </c>
       <c r="D73" s="3" t="s">
@@ -6352,7 +6349,7 @@
       <c r="B74" s="4">
         <v>45768</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C74" s="5">
         <v>45748</v>
       </c>
       <c r="D74" s="3" t="s">
@@ -6372,7 +6369,7 @@
       <c r="B75" s="4">
         <v>45762</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C75" s="5">
         <v>45748</v>
       </c>
       <c r="D75" s="3" t="s">
@@ -6392,7 +6389,7 @@
       <c r="B76" s="4">
         <v>45761</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76" s="5">
         <v>45748</v>
       </c>
       <c r="D76" s="3" t="s">
@@ -6412,7 +6409,7 @@
       <c r="B77" s="4">
         <v>45759</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C77" s="5">
         <v>45748</v>
       </c>
       <c r="D77" s="3" t="s">
@@ -6432,7 +6429,7 @@
       <c r="B78" s="4">
         <v>45753</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C78" s="5">
         <v>45748</v>
       </c>
       <c r="D78" s="3" t="s">
@@ -6452,7 +6449,7 @@
       <c r="B79" s="4">
         <v>45748</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79" s="5">
         <v>45748</v>
       </c>
       <c r="D79" s="3" t="s">
@@ -6472,7 +6469,7 @@
       <c r="B80" s="4">
         <v>45902</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="5">
         <v>45778</v>
       </c>
       <c r="D80" s="3" t="s">
@@ -6492,7 +6489,7 @@
       <c r="B81" s="4">
         <v>45855</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C81" s="5">
         <v>45778</v>
       </c>
       <c r="D81" s="3" t="s">
@@ -6512,7 +6509,7 @@
       <c r="B82" s="4">
         <v>45836</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82" s="5">
         <v>45778</v>
       </c>
       <c r="D82" s="3" t="s">
@@ -6532,7 +6529,7 @@
       <c r="B83" s="4">
         <v>45821</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C83" s="5">
         <v>45778</v>
       </c>
       <c r="D83" s="3" t="s">
@@ -6552,7 +6549,7 @@
       <c r="B84" s="4">
         <v>45805</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C84" s="5">
         <v>45778</v>
       </c>
       <c r="D84" s="3" t="s">
@@ -6572,7 +6569,7 @@
       <c r="B85" s="4">
         <v>45805</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C85" s="5">
         <v>45778</v>
       </c>
       <c r="D85" s="3" t="s">
@@ -6592,7 +6589,7 @@
       <c r="B86" s="4">
         <v>45804</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C86" s="5">
         <v>45778</v>
       </c>
       <c r="D86" s="3" t="s">
@@ -6612,7 +6609,7 @@
       <c r="B87" s="4">
         <v>45801</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C87" s="5">
         <v>45778</v>
       </c>
       <c r="D87" s="3" t="s">
@@ -6632,7 +6629,7 @@
       <c r="B88" s="4">
         <v>45800</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C88" s="5">
         <v>45778</v>
       </c>
       <c r="D88" s="3" t="s">
@@ -6652,7 +6649,7 @@
       <c r="B89" s="4">
         <v>45797</v>
       </c>
-      <c r="C89" s="6">
+      <c r="C89" s="5">
         <v>45778</v>
       </c>
       <c r="D89" s="3" t="s">
@@ -6672,7 +6669,7 @@
       <c r="B90" s="4">
         <v>45793</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90" s="5">
         <v>45778</v>
       </c>
       <c r="D90" s="3" t="s">
@@ -6692,7 +6689,7 @@
       <c r="B91" s="4">
         <v>45792</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C91" s="5">
         <v>45778</v>
       </c>
       <c r="D91" s="3" t="s">
@@ -6712,7 +6709,7 @@
       <c r="B92" s="4">
         <v>45790</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C92" s="5">
         <v>45778</v>
       </c>
       <c r="D92" s="3" t="s">
@@ -6732,7 +6729,7 @@
       <c r="B93" s="4">
         <v>45787</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93" s="5">
         <v>45778</v>
       </c>
       <c r="D93" s="3" t="s">
@@ -6752,7 +6749,7 @@
       <c r="B94" s="4">
         <v>45786</v>
       </c>
-      <c r="C94" s="6">
+      <c r="C94" s="5">
         <v>45778</v>
       </c>
       <c r="D94" s="3" t="s">
@@ -6772,7 +6769,7 @@
       <c r="B95" s="4">
         <v>45935</v>
       </c>
-      <c r="C95" s="6">
+      <c r="C95" s="5">
         <v>45809</v>
       </c>
       <c r="D95" s="3" t="s">
@@ -6792,7 +6789,7 @@
       <c r="B96" s="4">
         <v>45897</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C96" s="5">
         <v>45809</v>
       </c>
       <c r="D96" s="3" t="s">
@@ -6812,7 +6809,7 @@
       <c r="B97" s="4">
         <v>45849</v>
       </c>
-      <c r="C97" s="6">
+      <c r="C97" s="5">
         <v>45809</v>
       </c>
       <c r="D97" s="3" t="s">
@@ -6832,7 +6829,7 @@
       <c r="B98" s="4">
         <v>45832</v>
       </c>
-      <c r="C98" s="6">
+      <c r="C98" s="5">
         <v>45809</v>
       </c>
       <c r="D98" s="3" t="s">
@@ -6852,7 +6849,7 @@
       <c r="B99" s="4">
         <v>45829</v>
       </c>
-      <c r="C99" s="6">
+      <c r="C99" s="5">
         <v>45809</v>
       </c>
       <c r="D99" s="3" t="s">
@@ -6872,7 +6869,7 @@
       <c r="B100" s="4">
         <v>45819</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C100" s="5">
         <v>45809</v>
       </c>
       <c r="D100" s="3" t="s">
@@ -6892,7 +6889,7 @@
       <c r="B101" s="4">
         <v>45814</v>
       </c>
-      <c r="C101" s="6">
+      <c r="C101" s="5">
         <v>45809</v>
       </c>
       <c r="D101" s="3" t="s">
@@ -6912,7 +6909,7 @@
       <c r="B102" s="4">
         <v>45813</v>
       </c>
-      <c r="C102" s="6">
+      <c r="C102" s="5">
         <v>45809</v>
       </c>
       <c r="D102" s="3" t="s">
@@ -6932,7 +6929,7 @@
       <c r="B103" s="4">
         <v>45809</v>
       </c>
-      <c r="C103" s="6">
+      <c r="C103" s="5">
         <v>45809</v>
       </c>
       <c r="D103" s="3" t="s">
@@ -6952,7 +6949,7 @@
       <c r="B104" s="4">
         <v>45809</v>
       </c>
-      <c r="C104" s="6">
+      <c r="C104" s="5">
         <v>45809</v>
       </c>
       <c r="D104" s="3" t="s">
@@ -6972,7 +6969,7 @@
       <c r="B105" s="4">
         <v>45950</v>
       </c>
-      <c r="C105" s="6">
+      <c r="C105" s="5">
         <v>45839</v>
       </c>
       <c r="D105" s="3" t="s">
@@ -6992,7 +6989,7 @@
       <c r="B106" s="4">
         <v>45904</v>
       </c>
-      <c r="C106" s="6">
+      <c r="C106" s="5">
         <v>45839</v>
       </c>
       <c r="D106" s="3" t="s">
@@ -7012,7 +7009,7 @@
       <c r="B107" s="4">
         <v>45868</v>
       </c>
-      <c r="C107" s="6">
+      <c r="C107" s="5">
         <v>45839</v>
       </c>
       <c r="D107" s="3" t="s">
@@ -7032,7 +7029,7 @@
       <c r="B108" s="4">
         <v>45868</v>
       </c>
-      <c r="C108" s="6">
+      <c r="C108" s="5">
         <v>45839</v>
       </c>
       <c r="D108" s="3" t="s">
@@ -7052,7 +7049,7 @@
       <c r="B109" s="4">
         <v>45864</v>
       </c>
-      <c r="C109" s="6">
+      <c r="C109" s="5">
         <v>45839</v>
       </c>
       <c r="D109" s="3" t="s">
@@ -7072,7 +7069,7 @@
       <c r="B110" s="4">
         <v>45864</v>
       </c>
-      <c r="C110" s="6">
+      <c r="C110" s="5">
         <v>45839</v>
       </c>
       <c r="D110" s="3" t="s">
@@ -7092,7 +7089,7 @@
       <c r="B111" s="4">
         <v>45864</v>
       </c>
-      <c r="C111" s="6">
+      <c r="C111" s="5">
         <v>45839</v>
       </c>
       <c r="D111" s="3" t="s">
@@ -7112,7 +7109,7 @@
       <c r="B112" s="4">
         <v>45864</v>
       </c>
-      <c r="C112" s="6">
+      <c r="C112" s="5">
         <v>45839</v>
       </c>
       <c r="D112" s="3" t="s">
@@ -7132,7 +7129,7 @@
       <c r="B113" s="4">
         <v>45862</v>
       </c>
-      <c r="C113" s="6">
+      <c r="C113" s="5">
         <v>45839</v>
       </c>
       <c r="D113" s="3" t="s">
@@ -7152,7 +7149,7 @@
       <c r="B114" s="4">
         <v>45862</v>
       </c>
-      <c r="C114" s="6">
+      <c r="C114" s="5">
         <v>45839</v>
       </c>
       <c r="D114" s="3" t="s">
@@ -7172,7 +7169,7 @@
       <c r="B115" s="4">
         <v>45853</v>
       </c>
-      <c r="C115" s="6">
+      <c r="C115" s="5">
         <v>45839</v>
       </c>
       <c r="D115" s="3" t="s">
@@ -7192,7 +7189,7 @@
       <c r="B116" s="4">
         <v>45845</v>
       </c>
-      <c r="C116" s="6">
+      <c r="C116" s="5">
         <v>45839</v>
       </c>
       <c r="D116" s="3" t="s">
@@ -7212,7 +7209,7 @@
       <c r="B117" s="4">
         <v>45840</v>
       </c>
-      <c r="C117" s="6">
+      <c r="C117" s="5">
         <v>45839</v>
       </c>
       <c r="D117" s="3" t="s">
@@ -7232,7 +7229,7 @@
       <c r="B118" s="4">
         <v>45962</v>
       </c>
-      <c r="C118" s="6">
+      <c r="C118" s="5">
         <v>45870</v>
       </c>
       <c r="D118" s="3" t="s">
@@ -7252,7 +7249,7 @@
       <c r="B119" s="4">
         <v>45936</v>
       </c>
-      <c r="C119" s="6">
+      <c r="C119" s="5">
         <v>45870</v>
       </c>
       <c r="D119" s="3" t="s">
@@ -7272,7 +7269,7 @@
       <c r="B120" s="4">
         <v>45930</v>
       </c>
-      <c r="C120" s="6">
+      <c r="C120" s="5">
         <v>45870</v>
       </c>
       <c r="D120" s="3" t="s">
@@ -7292,7 +7289,7 @@
       <c r="B121" s="4">
         <v>45910</v>
       </c>
-      <c r="C121" s="6">
+      <c r="C121" s="5">
         <v>45870</v>
       </c>
       <c r="D121" s="3" t="s">
@@ -7312,7 +7309,7 @@
       <c r="B122" s="4">
         <v>45909</v>
       </c>
-      <c r="C122" s="6">
+      <c r="C122" s="5">
         <v>45870</v>
       </c>
       <c r="D122" s="3" t="s">
@@ -7332,7 +7329,7 @@
       <c r="B123" s="4">
         <v>45907</v>
       </c>
-      <c r="C123" s="6">
+      <c r="C123" s="5">
         <v>45870</v>
       </c>
       <c r="D123" s="3" t="s">
@@ -7352,7 +7349,7 @@
       <c r="B124" s="4">
         <v>45902</v>
       </c>
-      <c r="C124" s="6">
+      <c r="C124" s="5">
         <v>45870</v>
       </c>
       <c r="D124" s="3" t="s">
@@ -7372,7 +7369,7 @@
       <c r="B125" s="4">
         <v>45898</v>
       </c>
-      <c r="C125" s="6">
+      <c r="C125" s="5">
         <v>45870</v>
       </c>
       <c r="D125" s="3" t="s">
@@ -7392,7 +7389,7 @@
       <c r="B126" s="4">
         <v>45896</v>
       </c>
-      <c r="C126" s="6">
+      <c r="C126" s="5">
         <v>45870</v>
       </c>
       <c r="D126" s="3" t="s">
@@ -7412,7 +7409,7 @@
       <c r="B127" s="4">
         <v>45881</v>
       </c>
-      <c r="C127" s="6">
+      <c r="C127" s="5">
         <v>45870</v>
       </c>
       <c r="D127" s="3" t="s">
@@ -7432,7 +7429,7 @@
       <c r="B128" s="4">
         <v>45879</v>
       </c>
-      <c r="C128" s="6">
+      <c r="C128" s="5">
         <v>45870</v>
       </c>
       <c r="D128" s="3" t="s">
@@ -7445,14 +7442,14 @@
         <v>269</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="225" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="195" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B129" s="4">
         <v>45877</v>
       </c>
-      <c r="C129" s="6">
+      <c r="C129" s="5">
         <v>45870</v>
       </c>
       <c r="D129" s="3" t="s">
@@ -7472,7 +7469,7 @@
       <c r="B130" s="4">
         <v>45875</v>
       </c>
-      <c r="C130" s="6">
+      <c r="C130" s="5">
         <v>45870</v>
       </c>
       <c r="D130" s="3" t="s">
@@ -7492,7 +7489,7 @@
       <c r="B131" s="4">
         <v>45961</v>
       </c>
-      <c r="C131" s="6">
+      <c r="C131" s="5">
         <v>45901</v>
       </c>
       <c r="D131" s="3" t="s">
@@ -7512,7 +7509,7 @@
       <c r="B132" s="4">
         <v>45940</v>
       </c>
-      <c r="C132" s="6">
+      <c r="C132" s="5">
         <v>45901</v>
       </c>
       <c r="D132" s="3" t="s">
@@ -7532,7 +7529,7 @@
       <c r="B133" s="4">
         <v>45937</v>
       </c>
-      <c r="C133" s="6">
+      <c r="C133" s="5">
         <v>45901</v>
       </c>
       <c r="D133" s="3" t="s">
@@ -7552,7 +7549,7 @@
       <c r="B134" s="4">
         <v>45936</v>
       </c>
-      <c r="C134" s="6">
+      <c r="C134" s="5">
         <v>45901</v>
       </c>
       <c r="D134" s="3" t="s">
@@ -7572,7 +7569,7 @@
       <c r="B135" s="4">
         <v>45931</v>
       </c>
-      <c r="C135" s="6">
+      <c r="C135" s="5">
         <v>45901</v>
       </c>
       <c r="D135" s="3" t="s">
@@ -7592,7 +7589,7 @@
       <c r="B136" s="4">
         <v>45928</v>
       </c>
-      <c r="C136" s="6">
+      <c r="C136" s="5">
         <v>45901</v>
       </c>
       <c r="D136" s="3" t="s">
@@ -7612,7 +7609,7 @@
       <c r="B137" s="4">
         <v>45917</v>
       </c>
-      <c r="C137" s="6">
+      <c r="C137" s="5">
         <v>45901</v>
       </c>
       <c r="D137" s="3" t="s">
@@ -7625,14 +7622,14 @@
         <v>269</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B138" s="4">
         <v>45916</v>
       </c>
-      <c r="C138" s="6">
+      <c r="C138" s="5">
         <v>45901</v>
       </c>
       <c r="D138" s="3" t="s">
@@ -7652,7 +7649,7 @@
       <c r="B139" s="4">
         <v>45915</v>
       </c>
-      <c r="C139" s="6">
+      <c r="C139" s="5">
         <v>45901</v>
       </c>
       <c r="D139" s="3" t="s">
@@ -7672,7 +7669,7 @@
       <c r="B140" s="4">
         <v>45912</v>
       </c>
-      <c r="C140" s="6">
+      <c r="C140" s="5">
         <v>45901</v>
       </c>
       <c r="D140" s="3" t="s">
@@ -7692,7 +7689,7 @@
       <c r="B141" s="4">
         <v>45911</v>
       </c>
-      <c r="C141" s="6">
+      <c r="C141" s="5">
         <v>45901</v>
       </c>
       <c r="D141" s="3" t="s">
@@ -7712,7 +7709,7 @@
       <c r="B142" s="4">
         <v>45911</v>
       </c>
-      <c r="C142" s="6">
+      <c r="C142" s="5">
         <v>45901</v>
       </c>
       <c r="D142" s="3" t="s">
@@ -7732,7 +7729,7 @@
       <c r="B143" s="4">
         <v>45911</v>
       </c>
-      <c r="C143" s="6">
+      <c r="C143" s="5">
         <v>45901</v>
       </c>
       <c r="D143" s="3" t="s">
@@ -7752,7 +7749,7 @@
       <c r="B144" s="4">
         <v>45906</v>
       </c>
-      <c r="C144" s="6">
+      <c r="C144" s="5">
         <v>45901</v>
       </c>
       <c r="D144" s="3" t="s">
@@ -7772,7 +7769,7 @@
       <c r="B145" s="4">
         <v>45960</v>
       </c>
-      <c r="C145" s="6">
+      <c r="C145" s="5">
         <v>45931</v>
       </c>
       <c r="D145" s="3" t="s">
@@ -7792,7 +7789,7 @@
       <c r="B146" s="4">
         <v>45949</v>
       </c>
-      <c r="C146" s="6">
+      <c r="C146" s="5">
         <v>45931</v>
       </c>
       <c r="D146" s="3" t="s">
@@ -7812,7 +7809,7 @@
       <c r="B147" s="4">
         <v>45947</v>
       </c>
-      <c r="C147" s="6">
+      <c r="C147" s="5">
         <v>45931</v>
       </c>
       <c r="D147" s="3" t="s">
@@ -7832,7 +7829,7 @@
       <c r="B148" s="4">
         <v>45942</v>
       </c>
-      <c r="C148" s="6">
+      <c r="C148" s="5">
         <v>45931</v>
       </c>
       <c r="D148" s="3" t="s">
@@ -7852,7 +7849,7 @@
       <c r="B149" s="4">
         <v>45939</v>
       </c>
-      <c r="C149" s="6">
+      <c r="C149" s="5">
         <v>45931</v>
       </c>
       <c r="D149" s="3" t="s">
@@ -7872,7 +7869,7 @@
       <c r="B150" s="4">
         <v>45934</v>
       </c>
-      <c r="C150" s="6">
+      <c r="C150" s="5">
         <v>45931</v>
       </c>
       <c r="D150" s="3" t="s">
@@ -7892,7 +7889,7 @@
       <c r="B151" s="4">
         <v>45993</v>
       </c>
-      <c r="C151" s="6">
+      <c r="C151" s="5">
         <v>45962</v>
       </c>
       <c r="D151" s="3" t="s">
@@ -7912,7 +7909,7 @@
       <c r="B152" s="4">
         <v>45991</v>
       </c>
-      <c r="C152" s="6">
+      <c r="C152" s="5">
         <v>45962</v>
       </c>
       <c r="D152" s="3" t="s">
@@ -7932,7 +7929,7 @@
       <c r="B153" s="4">
         <v>45990</v>
       </c>
-      <c r="C153" s="6">
+      <c r="C153" s="5">
         <v>45962</v>
       </c>
       <c r="D153" s="3" t="s">
@@ -7952,7 +7949,7 @@
       <c r="B154" s="4">
         <v>45986</v>
       </c>
-      <c r="C154" s="6">
+      <c r="C154" s="5">
         <v>45962</v>
       </c>
       <c r="D154" s="3" t="s">
@@ -7972,7 +7969,7 @@
       <c r="B155" s="4">
         <v>45983</v>
       </c>
-      <c r="C155" s="6">
+      <c r="C155" s="5">
         <v>45962</v>
       </c>
       <c r="D155" s="3" t="s">
@@ -7992,7 +7989,7 @@
       <c r="B156" s="4">
         <v>45981</v>
       </c>
-      <c r="C156" s="6">
+      <c r="C156" s="5">
         <v>45962</v>
       </c>
       <c r="D156" s="3" t="s">
@@ -8012,7 +8009,7 @@
       <c r="B157" s="4">
         <v>45971</v>
       </c>
-      <c r="C157" s="6">
+      <c r="C157" s="5">
         <v>45962</v>
       </c>
       <c r="D157" s="3" t="s">
@@ -8032,7 +8029,7 @@
       <c r="B158" s="4">
         <v>45962</v>
       </c>
-      <c r="C158" s="6">
+      <c r="C158" s="5">
         <v>45962</v>
       </c>
       <c r="D158" s="3" t="s">
@@ -8052,7 +8049,7 @@
       <c r="B159" s="4">
         <v>46173</v>
       </c>
-      <c r="C159" s="6">
+      <c r="C159" s="5">
         <v>45992</v>
       </c>
       <c r="D159" s="3" t="s">
@@ -8072,7 +8069,7 @@
       <c r="B160" s="4">
         <v>46065</v>
       </c>
-      <c r="C160" s="6">
+      <c r="C160" s="5">
         <v>45992</v>
       </c>
       <c r="D160" s="3" t="s">
@@ -8092,7 +8089,7 @@
       <c r="B161" s="4">
         <v>46020</v>
       </c>
-      <c r="C161" s="6">
+      <c r="C161" s="5">
         <v>45992</v>
       </c>
       <c r="D161" s="3" t="s">
@@ -8112,7 +8109,7 @@
       <c r="B162" s="4">
         <v>46019</v>
       </c>
-      <c r="C162" s="6">
+      <c r="C162" s="5">
         <v>45992</v>
       </c>
       <c r="D162" s="3" t="s">
@@ -8132,7 +8129,7 @@
       <c r="B163" s="4">
         <v>46011</v>
       </c>
-      <c r="C163" s="6">
+      <c r="C163" s="5">
         <v>45992</v>
       </c>
       <c r="D163" s="3" t="s">
@@ -8152,7 +8149,7 @@
       <c r="B164" s="4">
         <v>46006</v>
       </c>
-      <c r="C164" s="6">
+      <c r="C164" s="5">
         <v>45992</v>
       </c>
       <c r="D164" s="3" t="s">
@@ -8172,7 +8169,7 @@
       <c r="B165" s="4">
         <v>46006</v>
       </c>
-      <c r="C165" s="6">
+      <c r="C165" s="5">
         <v>45992</v>
       </c>
       <c r="D165" s="3" t="s">
@@ -8192,7 +8189,7 @@
       <c r="B166" s="4">
         <v>46146</v>
       </c>
-      <c r="C166" s="6">
+      <c r="C166" s="5">
         <v>46023</v>
       </c>
       <c r="D166" s="3" t="s">
@@ -8212,7 +8209,7 @@
       <c r="B167" s="4">
         <v>46124</v>
       </c>
-      <c r="C167" s="6">
+      <c r="C167" s="5">
         <v>46023</v>
       </c>
       <c r="D167" s="3" t="s">
@@ -8232,7 +8229,7 @@
       <c r="B168" s="4">
         <v>46089</v>
       </c>
-      <c r="C168" s="6">
+      <c r="C168" s="5">
         <v>46023</v>
       </c>
       <c r="D168" s="3" t="s">
@@ -8252,7 +8249,7 @@
       <c r="B169" s="4">
         <v>46072</v>
       </c>
-      <c r="C169" s="6">
+      <c r="C169" s="5">
         <v>46023</v>
       </c>
       <c r="D169" s="3" t="s">
@@ -8272,7 +8269,7 @@
       <c r="B170" s="4">
         <v>46053</v>
       </c>
-      <c r="C170" s="6">
+      <c r="C170" s="5">
         <v>46023</v>
       </c>
       <c r="D170" s="3" t="s">
@@ -8292,7 +8289,7 @@
       <c r="B171" s="4">
         <v>46052</v>
       </c>
-      <c r="C171" s="6">
+      <c r="C171" s="5">
         <v>46023</v>
       </c>
       <c r="D171" s="3" t="s">
@@ -8312,7 +8309,7 @@
       <c r="B172" s="4">
         <v>46050</v>
       </c>
-      <c r="C172" s="6">
+      <c r="C172" s="5">
         <v>46023</v>
       </c>
       <c r="D172" s="3" t="s">
@@ -8332,7 +8329,7 @@
       <c r="B173" s="4">
         <v>46048</v>
       </c>
-      <c r="C173" s="6">
+      <c r="C173" s="5">
         <v>46023</v>
       </c>
       <c r="D173" s="3" t="s">
@@ -8352,7 +8349,7 @@
       <c r="B174" s="4">
         <v>46045</v>
       </c>
-      <c r="C174" s="6">
+      <c r="C174" s="5">
         <v>46023</v>
       </c>
       <c r="D174" s="3" t="s">
@@ -8372,7 +8369,7 @@
       <c r="B175" s="4">
         <v>46044</v>
       </c>
-      <c r="C175" s="6">
+      <c r="C175" s="5">
         <v>46023</v>
       </c>
       <c r="D175" s="3" t="s">
@@ -8392,7 +8389,7 @@
       <c r="B176" s="4">
         <v>46043</v>
       </c>
-      <c r="C176" s="6">
+      <c r="C176" s="5">
         <v>46023</v>
       </c>
       <c r="D176" s="3" t="s">
@@ -8412,7 +8409,7 @@
       <c r="B177" s="4">
         <v>46040</v>
       </c>
-      <c r="C177" s="6">
+      <c r="C177" s="5">
         <v>46023</v>
       </c>
       <c r="D177" s="3" t="s">
@@ -8432,7 +8429,7 @@
       <c r="B178" s="4">
         <v>46036</v>
       </c>
-      <c r="C178" s="6">
+      <c r="C178" s="5">
         <v>46023</v>
       </c>
       <c r="D178" s="3" t="s">
@@ -8452,7 +8449,7 @@
       <c r="B179" s="4">
         <v>46035</v>
       </c>
-      <c r="C179" s="6">
+      <c r="C179" s="5">
         <v>46023</v>
       </c>
       <c r="D179" s="3" t="s">
@@ -8472,7 +8469,7 @@
       <c r="B180" s="4">
         <v>46034</v>
       </c>
-      <c r="C180" s="6">
+      <c r="C180" s="5">
         <v>46023</v>
       </c>
       <c r="D180" s="3" t="s">
@@ -8492,7 +8489,7 @@
       <c r="B181" s="4">
         <v>46034</v>
       </c>
-      <c r="C181" s="6">
+      <c r="C181" s="5">
         <v>46023</v>
       </c>
       <c r="D181" s="3" t="s">
@@ -8512,7 +8509,7 @@
       <c r="B182" s="4">
         <v>46201</v>
       </c>
-      <c r="C182" s="6">
+      <c r="C182" s="5">
         <v>46054</v>
       </c>
       <c r="D182" s="3" t="s">
@@ -8532,7 +8529,7 @@
       <c r="B183" s="4">
         <v>46200</v>
       </c>
-      <c r="C183" s="6">
+      <c r="C183" s="5">
         <v>46054</v>
       </c>
       <c r="D183" s="3" t="s">
@@ -8552,7 +8549,7 @@
       <c r="B184" s="4">
         <v>46133</v>
       </c>
-      <c r="C184" s="6">
+      <c r="C184" s="5">
         <v>46054</v>
       </c>
       <c r="D184" s="3" t="s">
@@ -8572,7 +8569,7 @@
       <c r="B185" s="4">
         <v>46093</v>
       </c>
-      <c r="C185" s="6">
+      <c r="C185" s="5">
         <v>46054</v>
       </c>
       <c r="D185" s="3" t="s">
@@ -8592,7 +8589,7 @@
       <c r="B186" s="4">
         <v>46080</v>
       </c>
-      <c r="C186" s="6">
+      <c r="C186" s="5">
         <v>46054</v>
       </c>
       <c r="D186" s="3" t="s">
@@ -8612,7 +8609,7 @@
       <c r="B187" s="4">
         <v>46077</v>
       </c>
-      <c r="C187" s="6">
+      <c r="C187" s="5">
         <v>46054</v>
       </c>
       <c r="D187" s="3" t="s">
@@ -8632,7 +8629,7 @@
       <c r="B188" s="4">
         <v>46076</v>
       </c>
-      <c r="C188" s="6">
+      <c r="C188" s="5">
         <v>46054</v>
       </c>
       <c r="D188" s="3" t="s">
@@ -8652,7 +8649,7 @@
       <c r="B189" s="4">
         <v>46075</v>
       </c>
-      <c r="C189" s="6">
+      <c r="C189" s="5">
         <v>46054</v>
       </c>
       <c r="D189" s="3" t="s">
@@ -8672,7 +8669,7 @@
       <c r="B190" s="4">
         <v>46075</v>
       </c>
-      <c r="C190" s="6">
+      <c r="C190" s="5">
         <v>46054</v>
       </c>
       <c r="D190" s="3" t="s">
@@ -8692,7 +8689,7 @@
       <c r="B191" s="4">
         <v>46074</v>
       </c>
-      <c r="C191" s="6">
+      <c r="C191" s="5">
         <v>46054</v>
       </c>
       <c r="D191" s="3" t="s">
@@ -8705,14 +8702,14 @@
         <v>269</v>
       </c>
     </row>
-    <row r="192" spans="1:6" ht="300" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" ht="285" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
         <v>330</v>
       </c>
       <c r="B192" s="4">
         <v>46074</v>
       </c>
-      <c r="C192" s="6">
+      <c r="C192" s="5">
         <v>46054</v>
       </c>
       <c r="D192" s="3" t="s">
@@ -8732,7 +8729,7 @@
       <c r="B193" s="4">
         <v>46065</v>
       </c>
-      <c r="C193" s="6">
+      <c r="C193" s="5">
         <v>46054</v>
       </c>
       <c r="D193" s="3" t="s">
@@ -8752,7 +8749,7 @@
       <c r="B194" s="4">
         <v>46057</v>
       </c>
-      <c r="C194" s="6">
+      <c r="C194" s="5">
         <v>46054</v>
       </c>
       <c r="D194" s="3" t="s">
@@ -8772,7 +8769,7 @@
       <c r="B195" s="4">
         <v>46148</v>
       </c>
-      <c r="C195" s="6">
+      <c r="C195" s="5">
         <v>46082</v>
       </c>
       <c r="D195" s="3" t="s">
@@ -8792,7 +8789,7 @@
       <c r="B196" s="4">
         <v>46113</v>
       </c>
-      <c r="C196" s="6">
+      <c r="C196" s="5">
         <v>46082</v>
       </c>
       <c r="D196" s="3" t="s">
@@ -8812,7 +8809,7 @@
       <c r="B197" s="4">
         <v>46111</v>
       </c>
-      <c r="C197" s="6">
+      <c r="C197" s="5">
         <v>46082</v>
       </c>
       <c r="D197" s="3" t="s">
@@ -8832,7 +8829,7 @@
       <c r="B198" s="4">
         <v>46109</v>
       </c>
-      <c r="C198" s="6">
+      <c r="C198" s="5">
         <v>46082</v>
       </c>
       <c r="D198" s="3" t="s">
@@ -8852,7 +8849,7 @@
       <c r="B199" s="4">
         <v>46107</v>
       </c>
-      <c r="C199" s="6">
+      <c r="C199" s="5">
         <v>46082</v>
       </c>
       <c r="D199" s="3" t="s">
@@ -8872,7 +8869,7 @@
       <c r="B200" s="4">
         <v>46105</v>
       </c>
-      <c r="C200" s="6">
+      <c r="C200" s="5">
         <v>46082</v>
       </c>
       <c r="D200" s="3" t="s">
@@ -8892,7 +8889,7 @@
       <c r="B201" s="4">
         <v>46103</v>
       </c>
-      <c r="C201" s="6">
+      <c r="C201" s="5">
         <v>46082</v>
       </c>
       <c r="D201" s="3" t="s">
@@ -8912,7 +8909,7 @@
       <c r="B202" s="4">
         <v>46100</v>
       </c>
-      <c r="C202" s="6">
+      <c r="C202" s="5">
         <v>46082</v>
       </c>
       <c r="D202" s="3" t="s">
@@ -8932,7 +8929,7 @@
       <c r="B203" s="4">
         <v>46094</v>
       </c>
-      <c r="C203" s="6">
+      <c r="C203" s="5">
         <v>46082</v>
       </c>
       <c r="D203" s="3" t="s">
@@ -8952,7 +8949,7 @@
       <c r="B204" s="4">
         <v>46086</v>
       </c>
-      <c r="C204" s="6">
+      <c r="C204" s="5">
         <v>46082</v>
       </c>
       <c r="D204" s="3" t="s">
@@ -8972,7 +8969,7 @@
       <c r="B205" s="4">
         <v>46086</v>
       </c>
-      <c r="C205" s="6">
+      <c r="C205" s="5">
         <v>46082</v>
       </c>
       <c r="D205" s="3" t="s">
@@ -8992,7 +8989,7 @@
       <c r="B206" s="4">
         <v>46213</v>
       </c>
-      <c r="C206" s="6">
+      <c r="C206" s="5">
         <v>46113</v>
       </c>
       <c r="D206" s="3" t="s">
@@ -9012,7 +9009,7 @@
       <c r="B207" s="4">
         <v>46208</v>
       </c>
-      <c r="C207" s="6">
+      <c r="C207" s="5">
         <v>46113</v>
       </c>
       <c r="D207" s="3" t="s">
@@ -9032,7 +9029,7 @@
       <c r="B208" s="4">
         <v>46184</v>
       </c>
-      <c r="C208" s="6">
+      <c r="C208" s="5">
         <v>46113</v>
       </c>
       <c r="D208" s="3" t="s">
@@ -9052,7 +9049,7 @@
       <c r="B209" s="4">
         <v>46148</v>
       </c>
-      <c r="C209" s="6">
+      <c r="C209" s="5">
         <v>46113</v>
       </c>
       <c r="D209" s="3" t="s">
@@ -9072,7 +9069,7 @@
       <c r="B210" s="4">
         <v>46144</v>
       </c>
-      <c r="C210" s="6">
+      <c r="C210" s="5">
         <v>46113</v>
       </c>
       <c r="D210" s="3" t="s">
@@ -9092,7 +9089,7 @@
       <c r="B211" s="4">
         <v>46140</v>
       </c>
-      <c r="C211" s="6">
+      <c r="C211" s="5">
         <v>46113</v>
       </c>
       <c r="D211" s="3" t="s">
@@ -9112,7 +9109,7 @@
       <c r="B212" s="4">
         <v>46140</v>
       </c>
-      <c r="C212" s="6">
+      <c r="C212" s="5">
         <v>46113</v>
       </c>
       <c r="D212" s="3" t="s">
@@ -9132,7 +9129,7 @@
       <c r="B213" s="4">
         <v>46139</v>
       </c>
-      <c r="C213" s="6">
+      <c r="C213" s="5">
         <v>46113</v>
       </c>
       <c r="D213" s="3" t="s">
@@ -9152,7 +9149,7 @@
       <c r="B214" s="4">
         <v>46138</v>
       </c>
-      <c r="C214" s="6">
+      <c r="C214" s="5">
         <v>46113</v>
       </c>
       <c r="D214" s="3" t="s">
@@ -9172,7 +9169,7 @@
       <c r="B215" s="4">
         <v>46134</v>
       </c>
-      <c r="C215" s="6">
+      <c r="C215" s="5">
         <v>46113</v>
       </c>
       <c r="D215" s="3" t="s">
@@ -9192,7 +9189,7 @@
       <c r="B216" s="4">
         <v>46131</v>
       </c>
-      <c r="C216" s="6">
+      <c r="C216" s="5">
         <v>46113</v>
       </c>
       <c r="D216" s="3" t="s">
@@ -9212,7 +9209,7 @@
       <c r="B217" s="4">
         <v>46129</v>
       </c>
-      <c r="C217" s="6">
+      <c r="C217" s="5">
         <v>46113</v>
       </c>
       <c r="D217" s="3" t="s">
@@ -9232,7 +9229,7 @@
       <c r="B218" s="4">
         <v>46128</v>
       </c>
-      <c r="C218" s="6">
+      <c r="C218" s="5">
         <v>46113</v>
       </c>
       <c r="D218" s="3" t="s">
@@ -9252,7 +9249,7 @@
       <c r="B219" s="4">
         <v>46121</v>
       </c>
-      <c r="C219" s="6">
+      <c r="C219" s="5">
         <v>46113</v>
       </c>
       <c r="D219" s="3" t="s">
@@ -9272,7 +9269,7 @@
       <c r="B220" s="4">
         <v>46118</v>
       </c>
-      <c r="C220" s="6">
+      <c r="C220" s="5">
         <v>46113</v>
       </c>
       <c r="D220" s="3" t="s">
@@ -9292,7 +9289,7 @@
       <c r="B221" s="4">
         <v>46116</v>
       </c>
-      <c r="C221" s="6">
+      <c r="C221" s="5">
         <v>46113</v>
       </c>
       <c r="D221" s="3" t="s">
@@ -9312,7 +9309,7 @@
       <c r="B222" s="4">
         <v>46222</v>
       </c>
-      <c r="C222" s="6">
+      <c r="C222" s="5">
         <v>46143</v>
       </c>
       <c r="D222" s="3" t="s">
@@ -9332,7 +9329,7 @@
       <c r="B223" s="4">
         <v>46183</v>
       </c>
-      <c r="C223" s="6">
+      <c r="C223" s="5">
         <v>46143</v>
       </c>
       <c r="D223" s="3" t="s">
@@ -9352,7 +9349,7 @@
       <c r="B224" s="4">
         <v>46173</v>
       </c>
-      <c r="C224" s="6">
+      <c r="C224" s="5">
         <v>46143</v>
       </c>
       <c r="D224" s="3" t="s">
@@ -9372,7 +9369,7 @@
       <c r="B225" s="4">
         <v>46170</v>
       </c>
-      <c r="C225" s="6">
+      <c r="C225" s="5">
         <v>46143</v>
       </c>
       <c r="D225" s="3" t="s">
@@ -9392,7 +9389,7 @@
       <c r="B226" s="4">
         <v>46166</v>
       </c>
-      <c r="C226" s="6">
+      <c r="C226" s="5">
         <v>46143</v>
       </c>
       <c r="D226" s="3" t="s">
@@ -9412,7 +9409,7 @@
       <c r="B227" s="4">
         <v>46165</v>
       </c>
-      <c r="C227" s="6">
+      <c r="C227" s="5">
         <v>46143</v>
       </c>
       <c r="D227" s="3" t="s">
@@ -9432,7 +9429,7 @@
       <c r="B228" s="4">
         <v>46165</v>
       </c>
-      <c r="C228" s="6">
+      <c r="C228" s="5">
         <v>46143</v>
       </c>
       <c r="D228" s="3" t="s">
@@ -9452,7 +9449,7 @@
       <c r="B229" s="4">
         <v>46160</v>
       </c>
-      <c r="C229" s="6">
+      <c r="C229" s="5">
         <v>46143</v>
       </c>
       <c r="D229" s="3" t="s">
@@ -9472,7 +9469,7 @@
       <c r="B230" s="4">
         <v>46156</v>
       </c>
-      <c r="C230" s="6">
+      <c r="C230" s="5">
         <v>46143</v>
       </c>
       <c r="D230" s="3" t="s">
@@ -9492,7 +9489,7 @@
       <c r="B231" s="4">
         <v>46155</v>
       </c>
-      <c r="C231" s="6">
+      <c r="C231" s="5">
         <v>46143</v>
       </c>
       <c r="D231" s="3" t="s">
@@ -9512,7 +9509,7 @@
       <c r="B232" s="4">
         <v>46152</v>
       </c>
-      <c r="C232" s="6">
+      <c r="C232" s="5">
         <v>46143</v>
       </c>
       <c r="D232" s="3" t="s">
@@ -9532,7 +9529,7 @@
       <c r="B233" s="4">
         <v>46150</v>
       </c>
-      <c r="C233" s="6">
+      <c r="C233" s="5">
         <v>46143</v>
       </c>
       <c r="D233" s="3" t="s">
@@ -9552,7 +9549,7 @@
       <c r="B234" s="4">
         <v>46143</v>
       </c>
-      <c r="C234" s="6">
+      <c r="C234" s="5">
         <v>46143</v>
       </c>
       <c r="D234" s="3" t="s">
@@ -9572,7 +9569,7 @@
       <c r="B235" s="4">
         <v>46201</v>
       </c>
-      <c r="C235" s="6">
+      <c r="C235" s="5">
         <v>46174</v>
       </c>
       <c r="D235" s="3" t="s">
@@ -9592,7 +9589,7 @@
       <c r="B236" s="4">
         <v>46200</v>
       </c>
-      <c r="C236" s="6">
+      <c r="C236" s="5">
         <v>46174</v>
       </c>
       <c r="D236" s="3" t="s">
@@ -9612,7 +9609,7 @@
       <c r="B237" s="4">
         <v>46198</v>
       </c>
-      <c r="C237" s="6">
+      <c r="C237" s="5">
         <v>46174</v>
       </c>
       <c r="D237" s="3" t="s">
@@ -9632,7 +9629,7 @@
       <c r="B238" s="4">
         <v>46192</v>
       </c>
-      <c r="C238" s="6">
+      <c r="C238" s="5">
         <v>46174</v>
       </c>
       <c r="D238" s="3" t="s">
@@ -9652,7 +9649,7 @@
       <c r="B239" s="4">
         <v>46225</v>
       </c>
-      <c r="C239" s="6">
+      <c r="C239" s="5">
         <v>46204</v>
       </c>
       <c r="D239" s="3" t="s">
@@ -9672,7 +9669,7 @@
       <c r="B240" s="4">
         <v>46222</v>
       </c>
-      <c r="C240" s="6">
+      <c r="C240" s="5">
         <v>46204</v>
       </c>
       <c r="D240" s="3" t="s">
@@ -9692,7 +9689,7 @@
       <c r="B241" s="4">
         <v>46219</v>
       </c>
-      <c r="C241" s="6">
+      <c r="C241" s="5">
         <v>46204</v>
       </c>
       <c r="D241" s="3" t="s">
@@ -9712,7 +9709,7 @@
       <c r="B242" s="4">
         <v>46218</v>
       </c>
-      <c r="C242" s="6">
+      <c r="C242" s="5">
         <v>46204</v>
       </c>
       <c r="D242" s="3" t="s">
@@ -9732,7 +9729,7 @@
       <c r="B243" s="4">
         <v>46216</v>
       </c>
-      <c r="C243" s="6">
+      <c r="C243" s="5">
         <v>46204</v>
       </c>
       <c r="D243" s="3" t="s">
@@ -9752,7 +9749,7 @@
       <c r="B244" s="4">
         <v>46215</v>
       </c>
-      <c r="C244" s="6">
+      <c r="C244" s="5">
         <v>46204</v>
       </c>
       <c r="D244" s="3" t="s">
@@ -9772,7 +9769,7 @@
       <c r="B245" s="4">
         <v>46208</v>
       </c>
-      <c r="C245" s="6">
+      <c r="C245" s="5">
         <v>46204</v>
       </c>
       <c r="D245" s="3" t="s">
@@ -9792,7 +9789,7 @@
       <c r="B246" s="4">
         <v>46207</v>
       </c>
-      <c r="C246" s="6">
+      <c r="C246" s="5">
         <v>46204</v>
       </c>
       <c r="D246" s="3" t="s">
@@ -9812,7 +9809,7 @@
       <c r="B247" s="4">
         <v>45658</v>
       </c>
-      <c r="C247" s="6">
+      <c r="C247" s="5">
         <v>45658</v>
       </c>
       <c r="D247" s="3" t="s">
@@ -9831,7 +9828,7 @@
       <c r="B248" s="4">
         <v>45658</v>
       </c>
-      <c r="C248" s="6">
+      <c r="C248" s="5">
         <v>45658</v>
       </c>
       <c r="D248" s="3" t="s">
@@ -9850,7 +9847,7 @@
       <c r="B249" s="4">
         <v>45658</v>
       </c>
-      <c r="C249" s="6">
+      <c r="C249" s="5">
         <v>45658</v>
       </c>
       <c r="D249" s="3" t="s">
@@ -9869,7 +9866,7 @@
       <c r="B250" s="4">
         <v>45658</v>
       </c>
-      <c r="C250" s="6">
+      <c r="C250" s="5">
         <v>45658</v>
       </c>
       <c r="D250" s="3" t="s">
@@ -9888,7 +9885,7 @@
       <c r="B251" s="4">
         <v>45658</v>
       </c>
-      <c r="C251" s="6">
+      <c r="C251" s="5">
         <v>45658</v>
       </c>
       <c r="D251" s="3" t="s">
@@ -9907,7 +9904,7 @@
       <c r="B252" s="4">
         <v>45658</v>
       </c>
-      <c r="C252" s="6">
+      <c r="C252" s="5">
         <v>45658</v>
       </c>
       <c r="D252" s="3" t="s">
@@ -9926,7 +9923,7 @@
       <c r="B253" s="4">
         <v>45658</v>
       </c>
-      <c r="C253" s="6">
+      <c r="C253" s="5">
         <v>45658</v>
       </c>
       <c r="D253" s="3" t="s">
@@ -9945,7 +9942,7 @@
       <c r="B254" s="4">
         <v>45658</v>
       </c>
-      <c r="C254" s="6">
+      <c r="C254" s="5">
         <v>45658</v>
       </c>
       <c r="D254" s="3" t="s">
@@ -9964,7 +9961,7 @@
       <c r="B255" s="4">
         <v>45658</v>
       </c>
-      <c r="C255" s="6">
+      <c r="C255" s="5">
         <v>45658</v>
       </c>
       <c r="D255" s="3" t="s">
@@ -9983,7 +9980,7 @@
       <c r="B256" s="4">
         <v>45658</v>
       </c>
-      <c r="C256" s="6">
+      <c r="C256" s="5">
         <v>45658</v>
       </c>
       <c r="D256" s="3" t="s">
@@ -10002,7 +9999,7 @@
       <c r="B257" s="4">
         <v>45658</v>
       </c>
-      <c r="C257" s="6">
+      <c r="C257" s="5">
         <v>45658</v>
       </c>
       <c r="D257" s="3" t="s">
@@ -10021,7 +10018,7 @@
       <c r="B258" s="4">
         <v>45658</v>
       </c>
-      <c r="C258" s="6">
+      <c r="C258" s="5">
         <v>45658</v>
       </c>
       <c r="D258" s="3" t="s">
@@ -10040,7 +10037,7 @@
       <c r="B259" s="4">
         <v>45658</v>
       </c>
-      <c r="C259" s="6">
+      <c r="C259" s="5">
         <v>45658</v>
       </c>
       <c r="D259" s="3" t="s">
@@ -10059,7 +10056,7 @@
       <c r="B260" s="4">
         <v>45658</v>
       </c>
-      <c r="C260" s="6">
+      <c r="C260" s="5">
         <v>45658</v>
       </c>
       <c r="D260" s="3" t="s">
@@ -10071,14 +10068,14 @@
       <c r="G260"/>
       <c r="H260"/>
     </row>
-    <row r="261" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
         <v>326</v>
       </c>
       <c r="B261" s="4">
         <v>45689</v>
       </c>
-      <c r="C261" s="6">
+      <c r="C261" s="5">
         <v>45689</v>
       </c>
       <c r="D261" s="3" t="s">
@@ -10097,7 +10094,7 @@
       <c r="B262" s="4">
         <v>45689</v>
       </c>
-      <c r="C262" s="6">
+      <c r="C262" s="5">
         <v>45689</v>
       </c>
       <c r="D262" s="3" t="s">
@@ -10116,7 +10113,7 @@
       <c r="B263" s="4">
         <v>45689</v>
       </c>
-      <c r="C263" s="6">
+      <c r="C263" s="5">
         <v>45689</v>
       </c>
       <c r="D263" s="3" t="s">
@@ -10135,7 +10132,7 @@
       <c r="B264" s="4">
         <v>45689</v>
       </c>
-      <c r="C264" s="6">
+      <c r="C264" s="5">
         <v>45689</v>
       </c>
       <c r="D264" s="3" t="s">
@@ -10154,7 +10151,7 @@
       <c r="B265" s="4">
         <v>45689</v>
       </c>
-      <c r="C265" s="6">
+      <c r="C265" s="5">
         <v>45689</v>
       </c>
       <c r="D265" s="3" t="s">
@@ -10173,7 +10170,7 @@
       <c r="B266" s="4">
         <v>45689</v>
       </c>
-      <c r="C266" s="6">
+      <c r="C266" s="5">
         <v>45689</v>
       </c>
       <c r="D266" s="3" t="s">
@@ -10192,7 +10189,7 @@
       <c r="B267" s="4">
         <v>45689</v>
       </c>
-      <c r="C267" s="6">
+      <c r="C267" s="5">
         <v>45689</v>
       </c>
       <c r="D267" s="3" t="s">
@@ -10211,7 +10208,7 @@
       <c r="B268" s="4">
         <v>45689</v>
       </c>
-      <c r="C268" s="6">
+      <c r="C268" s="5">
         <v>45689</v>
       </c>
       <c r="D268" s="3" t="s">
@@ -10230,7 +10227,7 @@
       <c r="B269" s="4">
         <v>45689</v>
       </c>
-      <c r="C269" s="6">
+      <c r="C269" s="5">
         <v>45689</v>
       </c>
       <c r="D269" s="3" t="s">
@@ -10249,7 +10246,7 @@
       <c r="B270" s="4">
         <v>45689</v>
       </c>
-      <c r="C270" s="6">
+      <c r="C270" s="5">
         <v>45689</v>
       </c>
       <c r="D270" s="3" t="s">
@@ -10268,7 +10265,7 @@
       <c r="B271" s="4">
         <v>45717</v>
       </c>
-      <c r="C271" s="6">
+      <c r="C271" s="5">
         <v>45717</v>
       </c>
       <c r="D271" s="3" t="s">
@@ -10287,7 +10284,7 @@
       <c r="B272" s="4">
         <v>45717</v>
       </c>
-      <c r="C272" s="6">
+      <c r="C272" s="5">
         <v>45717</v>
       </c>
       <c r="D272" s="3" t="s">
@@ -10306,7 +10303,7 @@
       <c r="B273" s="4">
         <v>45717</v>
       </c>
-      <c r="C273" s="6">
+      <c r="C273" s="5">
         <v>45717</v>
       </c>
       <c r="D273" s="3" t="s">
@@ -10325,7 +10322,7 @@
       <c r="B274" s="4">
         <v>45717</v>
       </c>
-      <c r="C274" s="6">
+      <c r="C274" s="5">
         <v>45717</v>
       </c>
       <c r="D274" s="3" t="s">
@@ -10344,7 +10341,7 @@
       <c r="B275" s="4">
         <v>45717</v>
       </c>
-      <c r="C275" s="6">
+      <c r="C275" s="5">
         <v>45717</v>
       </c>
       <c r="D275" s="3" t="s">
@@ -10363,7 +10360,7 @@
       <c r="B276" s="4">
         <v>45717</v>
       </c>
-      <c r="C276" s="6">
+      <c r="C276" s="5">
         <v>45717</v>
       </c>
       <c r="D276" s="3" t="s">
@@ -10382,7 +10379,7 @@
       <c r="B277" s="4">
         <v>45717</v>
       </c>
-      <c r="C277" s="6">
+      <c r="C277" s="5">
         <v>45717</v>
       </c>
       <c r="D277" s="3" t="s">
@@ -10401,7 +10398,7 @@
       <c r="B278" s="4">
         <v>45717</v>
       </c>
-      <c r="C278" s="6">
+      <c r="C278" s="5">
         <v>45717</v>
       </c>
       <c r="D278" s="3" t="s">
@@ -10420,7 +10417,7 @@
       <c r="B279" s="4">
         <v>45717</v>
       </c>
-      <c r="C279" s="6">
+      <c r="C279" s="5">
         <v>45717</v>
       </c>
       <c r="D279" s="3" t="s">
@@ -10439,7 +10436,7 @@
       <c r="B280" s="4">
         <v>45717</v>
       </c>
-      <c r="C280" s="6">
+      <c r="C280" s="5">
         <v>45717</v>
       </c>
       <c r="D280" s="3" t="s">
@@ -10458,7 +10455,7 @@
       <c r="B281" s="4">
         <v>45717</v>
       </c>
-      <c r="C281" s="6">
+      <c r="C281" s="5">
         <v>45717</v>
       </c>
       <c r="D281" s="3" t="s">
@@ -10477,7 +10474,7 @@
       <c r="B282" s="4">
         <v>45748</v>
       </c>
-      <c r="C282" s="6">
+      <c r="C282" s="5">
         <v>45748</v>
       </c>
       <c r="D282" s="3" t="s">
@@ -10496,7 +10493,7 @@
       <c r="B283" s="4">
         <v>45748</v>
       </c>
-      <c r="C283" s="6">
+      <c r="C283" s="5">
         <v>45748</v>
       </c>
       <c r="D283" s="3" t="s">
@@ -10515,7 +10512,7 @@
       <c r="B284" s="4">
         <v>45748</v>
       </c>
-      <c r="C284" s="6">
+      <c r="C284" s="5">
         <v>45748</v>
       </c>
       <c r="D284" s="3" t="s">
@@ -10534,7 +10531,7 @@
       <c r="B285" s="4">
         <v>45748</v>
       </c>
-      <c r="C285" s="6">
+      <c r="C285" s="5">
         <v>45748</v>
       </c>
       <c r="D285" s="3" t="s">
@@ -10553,7 +10550,7 @@
       <c r="B286" s="4">
         <v>45748</v>
       </c>
-      <c r="C286" s="6">
+      <c r="C286" s="5">
         <v>45748</v>
       </c>
       <c r="D286" s="3" t="s">
@@ -10572,7 +10569,7 @@
       <c r="B287" s="4">
         <v>45778</v>
       </c>
-      <c r="C287" s="6">
+      <c r="C287" s="5">
         <v>45778</v>
       </c>
       <c r="D287" s="3" t="s">
@@ -10591,7 +10588,7 @@
       <c r="B288" s="4">
         <v>45778</v>
       </c>
-      <c r="C288" s="6">
+      <c r="C288" s="5">
         <v>45778</v>
       </c>
       <c r="D288" s="3" t="s">
@@ -10610,7 +10607,7 @@
       <c r="B289" s="4">
         <v>45778</v>
       </c>
-      <c r="C289" s="6">
+      <c r="C289" s="5">
         <v>45778</v>
       </c>
       <c r="D289" s="3" t="s">
@@ -10629,7 +10626,7 @@
       <c r="B290" s="4">
         <v>45778</v>
       </c>
-      <c r="C290" s="6">
+      <c r="C290" s="5">
         <v>45778</v>
       </c>
       <c r="D290" s="3" t="s">
@@ -10648,7 +10645,7 @@
       <c r="B291" s="4">
         <v>45809</v>
       </c>
-      <c r="C291" s="6">
+      <c r="C291" s="5">
         <v>45809</v>
       </c>
       <c r="D291" s="3" t="s">
@@ -10667,7 +10664,7 @@
       <c r="B292" s="4">
         <v>45809</v>
       </c>
-      <c r="C292" s="6">
+      <c r="C292" s="5">
         <v>45809</v>
       </c>
       <c r="D292" s="3" t="s">
@@ -10686,7 +10683,7 @@
       <c r="B293" s="4">
         <v>45839</v>
       </c>
-      <c r="C293" s="6">
+      <c r="C293" s="5">
         <v>45839</v>
       </c>
       <c r="D293" s="3" t="s">
@@ -10705,7 +10702,7 @@
       <c r="B294" s="4">
         <v>45839</v>
       </c>
-      <c r="C294" s="6">
+      <c r="C294" s="5">
         <v>45839</v>
       </c>
       <c r="D294" s="3" t="s">
@@ -10724,7 +10721,7 @@
       <c r="B295" s="4">
         <v>45839</v>
       </c>
-      <c r="C295" s="6">
+      <c r="C295" s="5">
         <v>45839</v>
       </c>
       <c r="D295" s="3" t="s">
@@ -10743,7 +10740,7 @@
       <c r="B296" s="4">
         <v>45870</v>
       </c>
-      <c r="C296" s="6">
+      <c r="C296" s="5">
         <v>45870</v>
       </c>
       <c r="D296" s="3" t="s">
@@ -10762,7 +10759,7 @@
       <c r="B297" s="4">
         <v>45901</v>
       </c>
-      <c r="C297" s="6">
+      <c r="C297" s="5">
         <v>45901</v>
       </c>
       <c r="D297" s="3" t="s">
@@ -10781,7 +10778,7 @@
       <c r="B298" s="4">
         <v>45901</v>
       </c>
-      <c r="C298" s="6">
+      <c r="C298" s="5">
         <v>45901</v>
       </c>
       <c r="D298" s="3" t="s">
@@ -10800,7 +10797,7 @@
       <c r="B299" s="4">
         <v>45901</v>
       </c>
-      <c r="C299" s="6">
+      <c r="C299" s="5">
         <v>45901</v>
       </c>
       <c r="D299" s="3" t="s">
@@ -10819,7 +10816,7 @@
       <c r="B300" s="4">
         <v>45901</v>
       </c>
-      <c r="C300" s="6">
+      <c r="C300" s="5">
         <v>45901</v>
       </c>
       <c r="D300" s="3" t="s">
@@ -10838,7 +10835,7 @@
       <c r="B301" s="4">
         <v>45931</v>
       </c>
-      <c r="C301" s="6">
+      <c r="C301" s="5">
         <v>45931</v>
       </c>
       <c r="D301" s="3" t="s">
@@ -10850,14 +10847,14 @@
       <c r="G301"/>
       <c r="H301"/>
     </row>
-    <row r="302" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" ht="180" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
         <v>326</v>
       </c>
       <c r="B302" s="4">
         <v>45931</v>
       </c>
-      <c r="C302" s="6">
+      <c r="C302" s="5">
         <v>45931</v>
       </c>
       <c r="D302" s="3" t="s">
@@ -10876,7 +10873,7 @@
       <c r="B303" s="4">
         <v>45931</v>
       </c>
-      <c r="C303" s="6">
+      <c r="C303" s="5">
         <v>45931</v>
       </c>
       <c r="D303" s="3" t="s">
@@ -10895,7 +10892,7 @@
       <c r="B304" s="4">
         <v>45962</v>
       </c>
-      <c r="C304" s="6">
+      <c r="C304" s="5">
         <v>45962</v>
       </c>
       <c r="D304" s="3" t="s">
@@ -10914,7 +10911,7 @@
       <c r="B305" s="4">
         <v>45962</v>
       </c>
-      <c r="C305" s="6">
+      <c r="C305" s="5">
         <v>45962</v>
       </c>
       <c r="D305" s="3" t="s">
@@ -10933,7 +10930,7 @@
       <c r="B306" s="4">
         <v>45962</v>
       </c>
-      <c r="C306" s="6">
+      <c r="C306" s="5">
         <v>45962</v>
       </c>
       <c r="D306" s="3" t="s">
@@ -10952,7 +10949,7 @@
       <c r="B307" s="4">
         <v>45962</v>
       </c>
-      <c r="C307" s="6">
+      <c r="C307" s="5">
         <v>45962</v>
       </c>
       <c r="D307" s="3" t="s">
@@ -10971,7 +10968,7 @@
       <c r="B308" s="4">
         <v>45962</v>
       </c>
-      <c r="C308" s="6">
+      <c r="C308" s="5">
         <v>45962</v>
       </c>
       <c r="D308" s="3" t="s">
@@ -10990,7 +10987,7 @@
       <c r="B309" s="4">
         <v>45992</v>
       </c>
-      <c r="C309" s="6">
+      <c r="C309" s="5">
         <v>45992</v>
       </c>
       <c r="D309" s="3" t="s">
@@ -11009,7 +11006,7 @@
       <c r="B310" s="4">
         <v>45992</v>
       </c>
-      <c r="C310" s="6">
+      <c r="C310" s="5">
         <v>45992</v>
       </c>
       <c r="D310" s="3" t="s">
@@ -11028,7 +11025,7 @@
       <c r="B311" s="4">
         <v>45992</v>
       </c>
-      <c r="C311" s="6">
+      <c r="C311" s="5">
         <v>45992</v>
       </c>
       <c r="D311" s="3" t="s">
@@ -11047,7 +11044,7 @@
       <c r="B312" s="4">
         <v>46023</v>
       </c>
-      <c r="C312" s="6">
+      <c r="C312" s="5">
         <v>46023</v>
       </c>
       <c r="D312" s="3" t="s">
@@ -11066,7 +11063,7 @@
       <c r="B313" s="4">
         <v>46023</v>
       </c>
-      <c r="C313" s="6">
+      <c r="C313" s="5">
         <v>46023</v>
       </c>
       <c r="D313" s="3" t="s">
@@ -11085,7 +11082,7 @@
       <c r="B314" s="4">
         <v>46023</v>
       </c>
-      <c r="C314" s="6">
+      <c r="C314" s="5">
         <v>46023</v>
       </c>
       <c r="D314" s="3" t="s">
@@ -11104,7 +11101,7 @@
       <c r="B315" s="4">
         <v>46023</v>
       </c>
-      <c r="C315" s="6">
+      <c r="C315" s="5">
         <v>46023</v>
       </c>
       <c r="D315" s="3" t="s">
@@ -11123,7 +11120,7 @@
       <c r="B316" s="4">
         <v>46023</v>
       </c>
-      <c r="C316" s="6">
+      <c r="C316" s="5">
         <v>46023</v>
       </c>
       <c r="D316" s="3" t="s">
@@ -11142,7 +11139,7 @@
       <c r="B317" s="4">
         <v>46023</v>
       </c>
-      <c r="C317" s="6">
+      <c r="C317" s="5">
         <v>46023</v>
       </c>
       <c r="D317" s="3" t="s">
@@ -11161,7 +11158,7 @@
       <c r="B318" s="4">
         <v>46023</v>
       </c>
-      <c r="C318" s="6">
+      <c r="C318" s="5">
         <v>46023</v>
       </c>
       <c r="D318" s="3" t="s">
@@ -11180,7 +11177,7 @@
       <c r="B319" s="4">
         <v>46023</v>
       </c>
-      <c r="C319" s="6">
+      <c r="C319" s="5">
         <v>46023</v>
       </c>
       <c r="D319" s="3" t="s">
@@ -11199,7 +11196,7 @@
       <c r="B320" s="4">
         <v>46023</v>
       </c>
-      <c r="C320" s="6">
+      <c r="C320" s="5">
         <v>46023</v>
       </c>
       <c r="D320" s="3" t="s">
@@ -11218,7 +11215,7 @@
       <c r="B321" s="4">
         <v>46054</v>
       </c>
-      <c r="C321" s="6">
+      <c r="C321" s="5">
         <v>46054</v>
       </c>
       <c r="D321" s="3" t="s">
@@ -11237,7 +11234,7 @@
       <c r="B322" s="4">
         <v>46054</v>
       </c>
-      <c r="C322" s="6">
+      <c r="C322" s="5">
         <v>46054</v>
       </c>
       <c r="D322" s="3" t="s">
@@ -11256,7 +11253,7 @@
       <c r="B323" s="4">
         <v>46054</v>
       </c>
-      <c r="C323" s="6">
+      <c r="C323" s="5">
         <v>46054</v>
       </c>
       <c r="D323" s="3" t="s">
@@ -11275,7 +11272,7 @@
       <c r="B324" s="4">
         <v>46054</v>
       </c>
-      <c r="C324" s="6">
+      <c r="C324" s="5">
         <v>46054</v>
       </c>
       <c r="D324" s="3" t="s">
@@ -11294,7 +11291,7 @@
       <c r="B325" s="4">
         <v>46054</v>
       </c>
-      <c r="C325" s="6">
+      <c r="C325" s="5">
         <v>46054</v>
       </c>
       <c r="D325" s="3" t="s">
@@ -11313,7 +11310,7 @@
       <c r="B326" s="4">
         <v>46054</v>
       </c>
-      <c r="C326" s="6">
+      <c r="C326" s="5">
         <v>46054</v>
       </c>
       <c r="D326" s="3" t="s">
@@ -11332,7 +11329,7 @@
       <c r="B327" s="4">
         <v>46082</v>
       </c>
-      <c r="C327" s="6">
+      <c r="C327" s="5">
         <v>46082</v>
       </c>
       <c r="D327" s="3" t="s">
@@ -11351,7 +11348,7 @@
       <c r="B328" s="4">
         <v>46082</v>
       </c>
-      <c r="C328" s="6">
+      <c r="C328" s="5">
         <v>46082</v>
       </c>
       <c r="D328" s="3" t="s">
@@ -11370,7 +11367,7 @@
       <c r="B329" s="4">
         <v>46082</v>
       </c>
-      <c r="C329" s="6">
+      <c r="C329" s="5">
         <v>46082</v>
       </c>
       <c r="D329" s="3" t="s">
@@ -11389,7 +11386,7 @@
       <c r="B330" s="4">
         <v>46082</v>
       </c>
-      <c r="C330" s="6">
+      <c r="C330" s="5">
         <v>46082</v>
       </c>
       <c r="D330" s="3" t="s">
@@ -11408,7 +11405,7 @@
       <c r="B331" s="4">
         <v>46082</v>
       </c>
-      <c r="C331" s="6">
+      <c r="C331" s="5">
         <v>46082</v>
       </c>
       <c r="D331" s="3" t="s">
@@ -11427,7 +11424,7 @@
       <c r="B332" s="4">
         <v>46082</v>
       </c>
-      <c r="C332" s="6">
+      <c r="C332" s="5">
         <v>46082</v>
       </c>
       <c r="D332" s="3" t="s">
@@ -11446,7 +11443,7 @@
       <c r="B333" s="4">
         <v>46082</v>
       </c>
-      <c r="C333" s="6">
+      <c r="C333" s="5">
         <v>46082</v>
       </c>
       <c r="D333" s="3" t="s">
@@ -11465,7 +11462,7 @@
       <c r="B334" s="4">
         <v>46082</v>
       </c>
-      <c r="C334" s="6">
+      <c r="C334" s="5">
         <v>46082</v>
       </c>
       <c r="D334" s="3" t="s">
@@ -11484,7 +11481,7 @@
       <c r="B335" s="4">
         <v>46113</v>
       </c>
-      <c r="C335" s="6">
+      <c r="C335" s="5">
         <v>46113</v>
       </c>
       <c r="D335" s="3" t="s">
@@ -11503,7 +11500,7 @@
       <c r="B336" s="4">
         <v>46113</v>
       </c>
-      <c r="C336" s="6">
+      <c r="C336" s="5">
         <v>46113</v>
       </c>
       <c r="D336" s="3" t="s">
@@ -11522,7 +11519,7 @@
       <c r="B337" s="4">
         <v>46113</v>
       </c>
-      <c r="C337" s="6">
+      <c r="C337" s="5">
         <v>46113</v>
       </c>
       <c r="D337" s="3" t="s">
@@ -11541,7 +11538,7 @@
       <c r="B338" s="4">
         <v>46113</v>
       </c>
-      <c r="C338" s="6">
+      <c r="C338" s="5">
         <v>46113</v>
       </c>
       <c r="D338" s="3" t="s">
@@ -11560,7 +11557,7 @@
       <c r="B339" s="4">
         <v>46113</v>
       </c>
-      <c r="C339" s="6">
+      <c r="C339" s="5">
         <v>46113</v>
       </c>
       <c r="D339" s="3" t="s">
@@ -11579,7 +11576,7 @@
       <c r="B340" s="4">
         <v>46113</v>
       </c>
-      <c r="C340" s="6">
+      <c r="C340" s="5">
         <v>46113</v>
       </c>
       <c r="D340" s="3" t="s">
@@ -11598,7 +11595,7 @@
       <c r="B341" s="4">
         <v>46113</v>
       </c>
-      <c r="C341" s="6">
+      <c r="C341" s="5">
         <v>46113</v>
       </c>
       <c r="D341" s="3" t="s">
@@ -11610,14 +11607,14 @@
       <c r="G341"/>
       <c r="H341"/>
     </row>
-    <row r="342" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
         <v>326</v>
       </c>
       <c r="B342" s="4">
         <v>46113</v>
       </c>
-      <c r="C342" s="6">
+      <c r="C342" s="5">
         <v>46113</v>
       </c>
       <c r="D342" s="3" t="s">
@@ -11636,7 +11633,7 @@
       <c r="B343" s="4">
         <v>46113</v>
       </c>
-      <c r="C343" s="6">
+      <c r="C343" s="5">
         <v>46113</v>
       </c>
       <c r="D343" s="3" t="s">
@@ -11655,7 +11652,7 @@
       <c r="B344" s="4">
         <v>46143</v>
       </c>
-      <c r="C344" s="6">
+      <c r="C344" s="5">
         <v>46143</v>
       </c>
       <c r="D344" s="3" t="s">
@@ -11674,7 +11671,7 @@
       <c r="B345" s="4">
         <v>46143</v>
       </c>
-      <c r="C345" s="6">
+      <c r="C345" s="5">
         <v>46143</v>
       </c>
       <c r="D345" s="3" t="s">
@@ -11686,14 +11683,14 @@
       <c r="G345"/>
       <c r="H345"/>
     </row>
-    <row r="346" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
         <v>326</v>
       </c>
       <c r="B346" s="4">
         <v>46143</v>
       </c>
-      <c r="C346" s="6">
+      <c r="C346" s="5">
         <v>46143</v>
       </c>
       <c r="D346" s="3" t="s">
@@ -11705,14 +11702,14 @@
       <c r="G346"/>
       <c r="H346"/>
     </row>
-    <row r="347" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A347" s="4" t="s">
         <v>326</v>
       </c>
       <c r="B347" s="4">
         <v>46143</v>
       </c>
-      <c r="C347" s="6">
+      <c r="C347" s="5">
         <v>46143</v>
       </c>
       <c r="D347" s="3" t="s">
@@ -11731,7 +11728,7 @@
       <c r="B348" s="4">
         <v>46143</v>
       </c>
-      <c r="C348" s="6">
+      <c r="C348" s="5">
         <v>46143</v>
       </c>
       <c r="D348" s="3" t="s">
@@ -11750,7 +11747,7 @@
       <c r="B349" s="4">
         <v>46143</v>
       </c>
-      <c r="C349" s="6">
+      <c r="C349" s="5">
         <v>46143</v>
       </c>
       <c r="D349" s="3" t="s">
@@ -11762,14 +11759,14 @@
       <c r="G349"/>
       <c r="H349"/>
     </row>
-    <row r="350" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A350" s="4" t="s">
         <v>326</v>
       </c>
       <c r="B350" s="4">
         <v>46174</v>
       </c>
-      <c r="C350" s="6">
+      <c r="C350" s="5">
         <v>46174</v>
       </c>
       <c r="D350" s="3" t="s">
@@ -11788,7 +11785,7 @@
       <c r="B351" s="4">
         <v>46174</v>
       </c>
-      <c r="C351" s="6">
+      <c r="C351" s="5">
         <v>46174</v>
       </c>
       <c r="D351" s="3" t="s">
@@ -11807,7 +11804,7 @@
       <c r="B352" s="4">
         <v>46204</v>
       </c>
-      <c r="C352" s="6">
+      <c r="C352" s="5">
         <v>46204</v>
       </c>
       <c r="D352" s="3" t="s">
@@ -11826,7 +11823,7 @@
       <c r="B353" s="4">
         <v>46204</v>
       </c>
-      <c r="C353" s="6">
+      <c r="C353" s="5">
         <v>46204</v>
       </c>
       <c r="D353" s="3" t="s">
@@ -11919,10 +11916,10 @@
       <c r="C4" s="2">
         <v>3.9</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>327</v>
       </c>
     </row>
